--- a/EGU26/GeoB4411-2_EGU26.xlsx
+++ b/EGU26/GeoB4411-2_EGU26.xlsx
@@ -27,8 +27,10 @@
     <sheet name="Series Id-1E1D79CD" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Series Id-D6812469" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Series Id-2DD42753" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="INTERPOLATION Id-F0BB8C98" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="SAMPLING Id-B18F0F5A" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Series Id-CB45AB6E" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="INTERPOLATION Id-F0BB8C98" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="SAMPLING Id-B18F0F5A" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="FILTER Id-D87F3640" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/04/30 at 14:21:11</t>
+          <t>Saved 2026/04/30 at 16:41:00</t>
         </is>
       </c>
     </row>
@@ -58229,6 +58231,6620 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L611"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="530" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MD2042_AgeAICC2012_d18OBtq_ka</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GeoB4411_PercAndes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>InterpolationMode</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>X1Coords</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>X2Coords</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>GeoB4411_depth_EM_cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B2" t="n">
+        <v/>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series filtered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#8c564b</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/30 at 15:02:08</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Imported series&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-1E1D79CD&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-1E1D79CD&lt;/i&gt;&lt;/b&gt; interpolated with INTERPOLATION &lt;i&gt;&lt;b&gt;Id-F0BB8C98&lt;/i&gt;&lt;/b&gt; with mode Linear&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-D6812469&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-D6812469&lt;/i&gt;&lt;/b&gt; sampled every 0.25 and linear interpolation with SAMPLING &lt;i&gt;&lt;b&gt;Id-B18F0F5A&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-2DD42753&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-2DD42753&lt;/i&gt;&lt;/b&gt; filtered with FILTER &lt;i&gt;&lt;b&gt;Id-D87F3640&lt;/i&gt;&lt;/b&gt; with a moving average of size 5&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-CB45AB6E&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="B3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>38.18</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>70.28866666666667</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="K4" t="n">
+        <v>89.91</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="B5" t="n">
+        <v>72.297</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.61</v>
+      </c>
+      <c r="K5" t="n">
+        <v>165.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>73.59333333333333</v>
+      </c>
+      <c r="J6" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="K6" t="n">
+        <v>207.54</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="B7" t="n">
+        <v>72.38066666666666</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="K7" t="n">
+        <v>260.88</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>70.73299999999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="K8" t="n">
+        <v>324.43</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="B9" t="n">
+        <v>69.31133333333334</v>
+      </c>
+      <c r="J9" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>67.50333333333333</v>
+      </c>
+      <c r="J10" t="n">
+        <v>102.76</v>
+      </c>
+      <c r="K10" t="n">
+        <v>441.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="B11" t="n">
+        <v>67.18300000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>111.31</v>
+      </c>
+      <c r="K11" t="n">
+        <v>462.34</v>
+      </c>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>68.08833333333334</v>
+      </c>
+      <c r="J12" t="n">
+        <v>116.48</v>
+      </c>
+      <c r="K12" t="n">
+        <v>470.58</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="B13" t="n">
+        <v>68.43900000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>130.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>481.65</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>68.65600000000001</v>
+      </c>
+      <c r="J14" t="n">
+        <v>133.77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>489.39</v>
+      </c>
+      <c r="L14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="B15" t="n">
+        <v>69.08266666666667</v>
+      </c>
+      <c r="J15" t="n">
+        <v>148.5765291287251</v>
+      </c>
+      <c r="K15" t="n">
+        <v>509.9124631713801</v>
+      </c>
+      <c r="L15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="n">
+        <v>68.93533333333333</v>
+      </c>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="B17" t="n">
+        <v>68.334</v>
+      </c>
+      <c r="L17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>67.63</v>
+      </c>
+      <c r="L18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="B19" t="n">
+        <v>67.066</v>
+      </c>
+      <c r="L19" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" t="n">
+        <v>67.114</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="B21" t="n">
+        <v>68.04400000000001</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>69.384</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="B23" t="n">
+        <v>69.833</v>
+      </c>
+      <c r="L23" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" t="n">
+        <v>69.45500000000001</v>
+      </c>
+      <c r="L24" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="B25" t="n">
+        <v>68.703</v>
+      </c>
+      <c r="L25" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>67.21266666666666</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="B27" t="n">
+        <v>65.39399999999999</v>
+      </c>
+      <c r="L27" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" t="n">
+        <v>64.98099999999999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="B29" t="n">
+        <v>65.60599999999999</v>
+      </c>
+      <c r="L29" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>65.71599999999998</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="B31" t="n">
+        <v>65.82899999999998</v>
+      </c>
+      <c r="L31" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="n">
+        <v>66.07000000000001</v>
+      </c>
+      <c r="L32" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="B33" t="n">
+        <v>66.29733333333333</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B34" t="n">
+        <v>66.389</v>
+      </c>
+      <c r="L34" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="B35" t="n">
+        <v>66.88699999999999</v>
+      </c>
+      <c r="L35" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="n">
+        <v>67.663</v>
+      </c>
+      <c r="L36" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="B37" t="n">
+        <v>68.73999999999999</v>
+      </c>
+      <c r="L37" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="B38" t="n">
+        <v>69.37866666666666</v>
+      </c>
+      <c r="L38" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="B39" t="n">
+        <v>69.62</v>
+      </c>
+      <c r="L39" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>69.622</v>
+      </c>
+      <c r="L40" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="L41" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B42" t="n">
+        <v>68.94866666666667</v>
+      </c>
+      <c r="L42" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="B43" t="n">
+        <v>68.744</v>
+      </c>
+      <c r="L43" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" t="n">
+        <v>68.60866666666666</v>
+      </c>
+      <c r="L44" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="B45" t="n">
+        <v>68.264</v>
+      </c>
+      <c r="L45" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="B46" t="n">
+        <v>68.48600000000002</v>
+      </c>
+      <c r="L46" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="B47" t="n">
+        <v>69.28666666666666</v>
+      </c>
+      <c r="L47" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>69.89</v>
+      </c>
+      <c r="L48" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="B49" t="n">
+        <v>70.47833333333334</v>
+      </c>
+      <c r="L49" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="B50" t="n">
+        <v>71.16233333333335</v>
+      </c>
+      <c r="L50" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="B51" t="n">
+        <v>71.355</v>
+      </c>
+      <c r="L51" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B52" t="n">
+        <v>71.31816666666667</v>
+      </c>
+      <c r="L52" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="B53" t="n">
+        <v>71.62649999999999</v>
+      </c>
+      <c r="L53" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>72.181</v>
+      </c>
+      <c r="L54" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="B55" t="n">
+        <v>72.90166666666667</v>
+      </c>
+      <c r="L55" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>17</v>
+      </c>
+      <c r="B56" t="n">
+        <v>72.23500000000001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="B57" t="n">
+        <v>71.13250000000001</v>
+      </c>
+      <c r="L57" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>70.82250000000001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="B59" t="n">
+        <v>70.38300000000001</v>
+      </c>
+      <c r="L59" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>18</v>
+      </c>
+      <c r="B60" t="n">
+        <v>69.28599999999999</v>
+      </c>
+      <c r="L60" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="B61" t="n">
+        <v>69.446</v>
+      </c>
+      <c r="L61" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>68.12899999999999</v>
+      </c>
+      <c r="L62" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="B63" t="n">
+        <v>65.20099999999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>19</v>
+      </c>
+      <c r="B64" t="n">
+        <v>66.027</v>
+      </c>
+      <c r="L64" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="B65" t="n">
+        <v>67.946</v>
+      </c>
+      <c r="L65" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>69.96099999999998</v>
+      </c>
+      <c r="L66" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="B67" t="n">
+        <v>73.58900000000001</v>
+      </c>
+      <c r="L67" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20</v>
+      </c>
+      <c r="B68" t="n">
+        <v>77.53412499999999</v>
+      </c>
+      <c r="L68" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="B69" t="n">
+        <v>77.636375</v>
+      </c>
+      <c r="L69" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>77.14475</v>
+      </c>
+      <c r="L70" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="B71" t="n">
+        <v>76.79425000000001</v>
+      </c>
+      <c r="L71" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>21</v>
+      </c>
+      <c r="B72" t="n">
+        <v>76.61187500000001</v>
+      </c>
+      <c r="L72" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="B73" t="n">
+        <v>76.71250000000001</v>
+      </c>
+      <c r="L73" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="B74" t="n">
+        <v>76.81312499999999</v>
+      </c>
+      <c r="L74" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="B75" t="n">
+        <v>76.91375000000001</v>
+      </c>
+      <c r="L75" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>22</v>
+      </c>
+      <c r="B76" t="n">
+        <v>77.014375</v>
+      </c>
+      <c r="L76" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="B77" t="n">
+        <v>77.11500000000001</v>
+      </c>
+      <c r="L77" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="B78" t="n">
+        <v>77.215625</v>
+      </c>
+      <c r="L78" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="B79" t="n">
+        <v>77.31625</v>
+      </c>
+      <c r="L79" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>23</v>
+      </c>
+      <c r="B80" t="n">
+        <v>77.416875</v>
+      </c>
+      <c r="L80" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="B81" t="n">
+        <v>77.51750000000001</v>
+      </c>
+      <c r="L81" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="B82" t="n">
+        <v>77.61812500000001</v>
+      </c>
+      <c r="L82" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="B83" t="n">
+        <v>77.48875000000001</v>
+      </c>
+      <c r="L83" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>24</v>
+      </c>
+      <c r="B84" t="n">
+        <v>77.32325</v>
+      </c>
+      <c r="L84" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="B85" t="n">
+        <v>76.65462500000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="B86" t="n">
+        <v>76.03387500000001</v>
+      </c>
+      <c r="L86" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="B87" t="n">
+        <v>75.33800000000001</v>
+      </c>
+      <c r="L87" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>25</v>
+      </c>
+      <c r="B88" t="n">
+        <v>75.28200000000001</v>
+      </c>
+      <c r="L88" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="B89" t="n">
+        <v>75.40600000000001</v>
+      </c>
+      <c r="L89" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="B90" t="n">
+        <v>75.729</v>
+      </c>
+      <c r="L90" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="B91" t="n">
+        <v>75.447</v>
+      </c>
+      <c r="L91" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>26</v>
+      </c>
+      <c r="B92" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="L92" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="B93" t="n">
+        <v>75.34700000000001</v>
+      </c>
+      <c r="L93" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="B94" t="n">
+        <v>74.34200000000001</v>
+      </c>
+      <c r="L94" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="B95" t="n">
+        <v>73.70000000000002</v>
+      </c>
+      <c r="L95" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>27</v>
+      </c>
+      <c r="B96" t="n">
+        <v>73.63900000000001</v>
+      </c>
+      <c r="L96" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="B97" t="n">
+        <v>73.13933333333333</v>
+      </c>
+      <c r="L97" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B98" t="n">
+        <v>72.43299999999999</v>
+      </c>
+      <c r="L98" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="B99" t="n">
+        <v>71.82599999999999</v>
+      </c>
+      <c r="L99" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>28</v>
+      </c>
+      <c r="B100" t="n">
+        <v>71.27200000000001</v>
+      </c>
+      <c r="L100" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="B101" t="n">
+        <v>71.18300000000002</v>
+      </c>
+      <c r="L101" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B102" t="n">
+        <v>71.46966666666667</v>
+      </c>
+      <c r="L102" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="B103" t="n">
+        <v>72.026</v>
+      </c>
+      <c r="L103" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>29</v>
+      </c>
+      <c r="B104" t="n">
+        <v>73.224</v>
+      </c>
+      <c r="L104" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="B105" t="n">
+        <v>74.369</v>
+      </c>
+      <c r="L105" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="B106" t="n">
+        <v>74.48399999999999</v>
+      </c>
+      <c r="L106" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="B107" t="n">
+        <v>74.306</v>
+      </c>
+      <c r="L107" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>30</v>
+      </c>
+      <c r="B108" t="n">
+        <v>73.923</v>
+      </c>
+      <c r="L108" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="B109" t="n">
+        <v>72.476</v>
+      </c>
+      <c r="L109" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B110" t="n">
+        <v>71.08799999999999</v>
+      </c>
+      <c r="L110" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="B111" t="n">
+        <v>71.06299999999999</v>
+      </c>
+      <c r="L111" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>31</v>
+      </c>
+      <c r="B112" t="n">
+        <v>70.502</v>
+      </c>
+      <c r="L112" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="B113" t="n">
+        <v>70.11799999999998</v>
+      </c>
+      <c r="L113" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="B114" t="n">
+        <v>70.28399999999999</v>
+      </c>
+      <c r="L114" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="B115" t="n">
+        <v>70.53700000000001</v>
+      </c>
+      <c r="L115" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>32</v>
+      </c>
+      <c r="B116" t="n">
+        <v>70.375</v>
+      </c>
+      <c r="L116" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="B117" t="n">
+        <v>70.65599999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="B118" t="n">
+        <v>71.087</v>
+      </c>
+      <c r="L118" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="B119" t="n">
+        <v>71.41400000000002</v>
+      </c>
+      <c r="L119" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>33</v>
+      </c>
+      <c r="B120" t="n">
+        <v>71.99600000000001</v>
+      </c>
+      <c r="L120" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="B121" t="n">
+        <v>70.97200000000001</v>
+      </c>
+      <c r="L121" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B122" t="n">
+        <v>69.702</v>
+      </c>
+      <c r="L122" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="B123" t="n">
+        <v>69.21900000000001</v>
+      </c>
+      <c r="L123" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>34</v>
+      </c>
+      <c r="B124" t="n">
+        <v>69.76300000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="B125" t="n">
+        <v>69.679</v>
+      </c>
+      <c r="L125" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="B126" t="n">
+        <v>69.90600000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="B127" t="n">
+        <v>69.88000000000001</v>
+      </c>
+      <c r="L127" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>35</v>
+      </c>
+      <c r="B128" t="n">
+        <v>70.30199999999999</v>
+      </c>
+      <c r="L128" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="B129" t="n">
+        <v>70.217</v>
+      </c>
+      <c r="L129" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B130" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="L130" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="B131" t="n">
+        <v>70.33099999999999</v>
+      </c>
+      <c r="L131" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>36</v>
+      </c>
+      <c r="B132" t="n">
+        <v>71.43199999999999</v>
+      </c>
+      <c r="L132" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="B133" t="n">
+        <v>71.16799999999999</v>
+      </c>
+      <c r="L133" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B134" t="n">
+        <v>70.71799999999999</v>
+      </c>
+      <c r="L134" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="B135" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="L135" t="n">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>37</v>
+      </c>
+      <c r="B136" t="n">
+        <v>71.295</v>
+      </c>
+      <c r="L136" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="B137" t="n">
+        <v>71.68100000000001</v>
+      </c>
+      <c r="L137" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="B138" t="n">
+        <v>72.11300000000001</v>
+      </c>
+      <c r="L138" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="B139" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="L139" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>38</v>
+      </c>
+      <c r="B140" t="n">
+        <v>72.69500000000001</v>
+      </c>
+      <c r="L140" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="B141" t="n">
+        <v>72.566</v>
+      </c>
+      <c r="L141" t="n">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="B142" t="n">
+        <v>72.5295</v>
+      </c>
+      <c r="L142" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="B143" t="n">
+        <v>72.58450000000001</v>
+      </c>
+      <c r="L143" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>39</v>
+      </c>
+      <c r="B144" t="n">
+        <v>70.59549999999999</v>
+      </c>
+      <c r="L144" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="B145" t="n">
+        <v>69.41499999999999</v>
+      </c>
+      <c r="L145" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B146" t="n">
+        <v>69.30850000000001</v>
+      </c>
+      <c r="L146" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="B147" t="n">
+        <v>69.301</v>
+      </c>
+      <c r="L147" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>40</v>
+      </c>
+      <c r="B148" t="n">
+        <v>69.07849999999999</v>
+      </c>
+      <c r="L148" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="B149" t="n">
+        <v>71.083</v>
+      </c>
+      <c r="L149" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="B150" t="n">
+        <v>72.66249999999999</v>
+      </c>
+      <c r="L150" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="B151" t="n">
+        <v>73</v>
+      </c>
+      <c r="L151" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>41</v>
+      </c>
+      <c r="B152" t="n">
+        <v>73</v>
+      </c>
+      <c r="L152" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="B153" t="n">
+        <v>73.44000000000001</v>
+      </c>
+      <c r="L153" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="B154" t="n">
+        <v>73.52549999999999</v>
+      </c>
+      <c r="L154" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="B155" t="n">
+        <v>73.0265</v>
+      </c>
+      <c r="L155" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>42</v>
+      </c>
+      <c r="B156" t="n">
+        <v>72.54349999999999</v>
+      </c>
+      <c r="L156" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="B157" t="n">
+        <v>72.381</v>
+      </c>
+      <c r="L157" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B158" t="n">
+        <v>71.999</v>
+      </c>
+      <c r="L158" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="B159" t="n">
+        <v>71.84949999999999</v>
+      </c>
+      <c r="L159" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>43</v>
+      </c>
+      <c r="B160" t="n">
+        <v>71.8015</v>
+      </c>
+      <c r="L160" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="B161" t="n">
+        <v>72.76349999999999</v>
+      </c>
+      <c r="L161" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="B162" t="n">
+        <v>73.072</v>
+      </c>
+      <c r="L162" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="B163" t="n">
+        <v>73.4783</v>
+      </c>
+      <c r="L163" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>44</v>
+      </c>
+      <c r="B164" t="n">
+        <v>74.0744</v>
+      </c>
+      <c r="L164" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="B165" t="n">
+        <v>75.0748</v>
+      </c>
+      <c r="L165" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="B166" t="n">
+        <v>75.60299999999999</v>
+      </c>
+      <c r="L166" t="n">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="B167" t="n">
+        <v>76.71799999999999</v>
+      </c>
+      <c r="L167" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>45</v>
+      </c>
+      <c r="B168" t="n">
+        <v>77.22819999999999</v>
+      </c>
+      <c r="L168" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="B169" t="n">
+        <v>77.32159999999999</v>
+      </c>
+      <c r="L169" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="B170" t="n">
+        <v>76.20920000000001</v>
+      </c>
+      <c r="L170" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="B171" t="n">
+        <v>75.27099999999999</v>
+      </c>
+      <c r="L171" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>46</v>
+      </c>
+      <c r="B172" t="n">
+        <v>73.16200000000001</v>
+      </c>
+      <c r="L172" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="B173" t="n">
+        <v>70.583</v>
+      </c>
+      <c r="L173" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="B174" t="n">
+        <v>69.14099999999999</v>
+      </c>
+      <c r="L174" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="B175" t="n">
+        <v>69.595</v>
+      </c>
+      <c r="L175" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>47</v>
+      </c>
+      <c r="B176" t="n">
+        <v>69.696</v>
+      </c>
+      <c r="L176" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="B177" t="n">
+        <v>70.79600000000001</v>
+      </c>
+      <c r="L177" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="B178" t="n">
+        <v>72.63000000000001</v>
+      </c>
+      <c r="L178" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="B179" t="n">
+        <v>73.33599999999998</v>
+      </c>
+      <c r="L179" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>48</v>
+      </c>
+      <c r="B180" t="n">
+        <v>73.65200000000002</v>
+      </c>
+      <c r="L180" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="B181" t="n">
+        <v>73.91799999999998</v>
+      </c>
+      <c r="L181" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B182" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="L182" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="B183" t="n">
+        <v>74.59099999999999</v>
+      </c>
+      <c r="L183" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>49</v>
+      </c>
+      <c r="B184" t="n">
+        <v>74.134</v>
+      </c>
+      <c r="L184" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="B185" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="L185" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="B186" t="n">
+        <v>72.56300000000002</v>
+      </c>
+      <c r="L186" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="B187" t="n">
+        <v>71.699</v>
+      </c>
+      <c r="L187" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>50</v>
+      </c>
+      <c r="B188" t="n">
+        <v>71.30799999999999</v>
+      </c>
+      <c r="L188" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="B189" t="n">
+        <v>71.88300000000001</v>
+      </c>
+      <c r="L189" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="B190" t="n">
+        <v>71.914</v>
+      </c>
+      <c r="L190" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="B191" t="n">
+        <v>71.51000000000001</v>
+      </c>
+      <c r="L191" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>51</v>
+      </c>
+      <c r="B192" t="n">
+        <v>71.58999999999999</v>
+      </c>
+      <c r="L192" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="B193" t="n">
+        <v>71.55499999999999</v>
+      </c>
+      <c r="L193" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="B194" t="n">
+        <v>71.05199999999999</v>
+      </c>
+      <c r="L194" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="B195" t="n">
+        <v>71.00699999999999</v>
+      </c>
+      <c r="L195" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>52</v>
+      </c>
+      <c r="B196" t="n">
+        <v>71.39399999999999</v>
+      </c>
+      <c r="L196" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="B197" t="n">
+        <v>71.27099999999999</v>
+      </c>
+      <c r="L197" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="B198" t="n">
+        <v>70.798</v>
+      </c>
+      <c r="L198" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="B199" t="n">
+        <v>70.72999999999999</v>
+      </c>
+      <c r="L199" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>53</v>
+      </c>
+      <c r="B200" t="n">
+        <v>70.56</v>
+      </c>
+      <c r="L200" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="B201" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="L201" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B202" t="n">
+        <v>69.55799999999999</v>
+      </c>
+      <c r="L202" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="B203" t="n">
+        <v>69.408</v>
+      </c>
+      <c r="L203" t="n">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>54</v>
+      </c>
+      <c r="B204" t="n">
+        <v>69.40799999999999</v>
+      </c>
+      <c r="L204" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="B205" t="n">
+        <v>69.29599999999999</v>
+      </c>
+      <c r="L205" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="B206" t="n">
+        <v>69.16900000000001</v>
+      </c>
+      <c r="L206" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="B207" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="L207" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>55</v>
+      </c>
+      <c r="B208" t="n">
+        <v>68.72</v>
+      </c>
+      <c r="L208" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="B209" t="n">
+        <v>67.904</v>
+      </c>
+      <c r="L209" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="B210" t="n">
+        <v>67.041</v>
+      </c>
+      <c r="L210" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="B211" t="n">
+        <v>66.333</v>
+      </c>
+      <c r="L211" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>56</v>
+      </c>
+      <c r="B212" t="n">
+        <v>65.59699999999999</v>
+      </c>
+      <c r="L212" t="n">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="B213" t="n">
+        <v>64.38199999999999</v>
+      </c>
+      <c r="L213" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="B214" t="n">
+        <v>63.64599999999999</v>
+      </c>
+      <c r="L214" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="B215" t="n">
+        <v>64.435</v>
+      </c>
+      <c r="L215" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>57</v>
+      </c>
+      <c r="B216" t="n">
+        <v>65.30800000000001</v>
+      </c>
+      <c r="L216" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="B217" t="n">
+        <v>66.038</v>
+      </c>
+      <c r="L217" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="B218" t="n">
+        <v>67.35299999999999</v>
+      </c>
+      <c r="L218" t="n">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="B219" t="n">
+        <v>68.48299999999999</v>
+      </c>
+      <c r="L219" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>58</v>
+      </c>
+      <c r="B220" t="n">
+        <v>68.24100000000001</v>
+      </c>
+      <c r="L220" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="B221" t="n">
+        <v>67.727</v>
+      </c>
+      <c r="L221" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="B222" t="n">
+        <v>67.67699999999999</v>
+      </c>
+      <c r="L222" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="B223" t="n">
+        <v>67.735</v>
+      </c>
+      <c r="L223" t="n">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>59</v>
+      </c>
+      <c r="B224" t="n">
+        <v>67.90299999999999</v>
+      </c>
+      <c r="L224" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="B225" t="n">
+        <v>68.08800000000001</v>
+      </c>
+      <c r="L225" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="B226" t="n">
+        <v>68.40700000000001</v>
+      </c>
+      <c r="L226" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="B227" t="n">
+        <v>68.825</v>
+      </c>
+      <c r="L227" t="n">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>60</v>
+      </c>
+      <c r="B228" t="n">
+        <v>69.114</v>
+      </c>
+      <c r="L228" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="B229" t="n">
+        <v>69.188</v>
+      </c>
+      <c r="L229" t="n">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="B230" t="n">
+        <v>69.29100000000001</v>
+      </c>
+      <c r="L230" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="B231" t="n">
+        <v>69.155</v>
+      </c>
+      <c r="L231" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>61</v>
+      </c>
+      <c r="B232" t="n">
+        <v>69.128</v>
+      </c>
+      <c r="L232" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="B233" t="n">
+        <v>69.202</v>
+      </c>
+      <c r="L233" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="B234" t="n">
+        <v>69.404</v>
+      </c>
+      <c r="L234" t="n">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="B235" t="n">
+        <v>68.369</v>
+      </c>
+      <c r="L235" t="n">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>62</v>
+      </c>
+      <c r="B236" t="n">
+        <v>67.423</v>
+      </c>
+      <c r="L236" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="B237" t="n">
+        <v>66.38300000000001</v>
+      </c>
+      <c r="L237" t="n">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="B238" t="n">
+        <v>65.595</v>
+      </c>
+      <c r="L238" t="n">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="B239" t="n">
+        <v>66.105</v>
+      </c>
+      <c r="L239" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>63</v>
+      </c>
+      <c r="B240" t="n">
+        <v>68.24300000000001</v>
+      </c>
+      <c r="L240" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="B241" t="n">
+        <v>70.155</v>
+      </c>
+      <c r="L241" t="n">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="B242" t="n">
+        <v>71.759</v>
+      </c>
+      <c r="L242" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="B243" t="n">
+        <v>72.744</v>
+      </c>
+      <c r="L243" t="n">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>64</v>
+      </c>
+      <c r="B244" t="n">
+        <v>72.38700000000001</v>
+      </c>
+      <c r="L244" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="B245" t="n">
+        <v>71.899</v>
+      </c>
+      <c r="L245" t="n">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="B246" t="n">
+        <v>71.81399999999999</v>
+      </c>
+      <c r="L246" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="B247" t="n">
+        <v>71.639</v>
+      </c>
+      <c r="L247" t="n">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>65</v>
+      </c>
+      <c r="B248" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="L248" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="B249" t="n">
+        <v>72.06399999999999</v>
+      </c>
+      <c r="L249" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="B250" t="n">
+        <v>72.426</v>
+      </c>
+      <c r="L250" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="B251" t="n">
+        <v>72.965</v>
+      </c>
+      <c r="L251" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>66</v>
+      </c>
+      <c r="B252" t="n">
+        <v>73.437</v>
+      </c>
+      <c r="L252" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="B253" t="n">
+        <v>73.479</v>
+      </c>
+      <c r="L253" t="n">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B254" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="L254" t="n">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="B255" t="n">
+        <v>73.499</v>
+      </c>
+      <c r="L255" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>67</v>
+      </c>
+      <c r="B256" t="n">
+        <v>73.858</v>
+      </c>
+      <c r="L256" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="B257" t="n">
+        <v>74.43899999999999</v>
+      </c>
+      <c r="L257" t="n">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="B258" t="n">
+        <v>75.76300000000001</v>
+      </c>
+      <c r="L258" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="B259" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="L259" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>68</v>
+      </c>
+      <c r="B260" t="n">
+        <v>77.48466666666666</v>
+      </c>
+      <c r="L260" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="B261" t="n">
+        <v>77.684</v>
+      </c>
+      <c r="L261" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="B262" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="L262" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="B263" t="n">
+        <v>76.676</v>
+      </c>
+      <c r="L263" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>69</v>
+      </c>
+      <c r="B264" t="n">
+        <v>76.59700000000001</v>
+      </c>
+      <c r="L264" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="B265" t="n">
+        <v>76.67133333333332</v>
+      </c>
+      <c r="L265" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="B266" t="n">
+        <v>76.55600000000001</v>
+      </c>
+      <c r="L266" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="B267" t="n">
+        <v>76.191</v>
+      </c>
+      <c r="L267" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>70</v>
+      </c>
+      <c r="B268" t="n">
+        <v>76.19800000000001</v>
+      </c>
+      <c r="L268" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="B269" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="L269" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="B270" t="n">
+        <v>75.46200000000002</v>
+      </c>
+      <c r="L270" t="n">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="B271" t="n">
+        <v>74.71900000000001</v>
+      </c>
+      <c r="L271" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>71</v>
+      </c>
+      <c r="B272" t="n">
+        <v>74.983</v>
+      </c>
+      <c r="L272" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="B273" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="L273" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="B274" t="n">
+        <v>73.73899999999999</v>
+      </c>
+      <c r="L274" t="n">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="B275" t="n">
+        <v>73.39200000000001</v>
+      </c>
+      <c r="L275" t="n">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>72</v>
+      </c>
+      <c r="B276" t="n">
+        <v>73.29400000000001</v>
+      </c>
+      <c r="L276" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="B277" t="n">
+        <v>72.86999999999999</v>
+      </c>
+      <c r="L277" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="B278" t="n">
+        <v>72.905</v>
+      </c>
+      <c r="L278" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="B279" t="n">
+        <v>73.271</v>
+      </c>
+      <c r="L279" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>73</v>
+      </c>
+      <c r="B280" t="n">
+        <v>73.372</v>
+      </c>
+      <c r="L280" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="B281" t="n">
+        <v>73.744</v>
+      </c>
+      <c r="L281" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="B282" t="n">
+        <v>73.473</v>
+      </c>
+      <c r="L282" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="B283" t="n">
+        <v>72.833</v>
+      </c>
+      <c r="L283" t="n">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>74</v>
+      </c>
+      <c r="B284" t="n">
+        <v>72.35799999999999</v>
+      </c>
+      <c r="L284" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="B285" t="n">
+        <v>71.529</v>
+      </c>
+      <c r="L285" t="n">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="B286" t="n">
+        <v>70.575</v>
+      </c>
+      <c r="L286" t="n">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="B287" t="n">
+        <v>70.496</v>
+      </c>
+      <c r="L287" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>75</v>
+      </c>
+      <c r="B288" t="n">
+        <v>69.804</v>
+      </c>
+      <c r="L288" t="n">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="B289" t="n">
+        <v>69.14200000000001</v>
+      </c>
+      <c r="L289" t="n">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="B290" t="n">
+        <v>69.236</v>
+      </c>
+      <c r="L290" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="B291" t="n">
+        <v>69.779</v>
+      </c>
+      <c r="L291" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>76</v>
+      </c>
+      <c r="B292" t="n">
+        <v>70.03400000000002</v>
+      </c>
+      <c r="L292" t="n">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="B293" t="n">
+        <v>70.85499999999999</v>
+      </c>
+      <c r="L293" t="n">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="B294" t="n">
+        <v>71.68300000000001</v>
+      </c>
+      <c r="L294" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="B295" t="n">
+        <v>72.473</v>
+      </c>
+      <c r="L295" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>77</v>
+      </c>
+      <c r="B296" t="n">
+        <v>72.304</v>
+      </c>
+      <c r="L296" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="B297" t="n">
+        <v>71.94300000000001</v>
+      </c>
+      <c r="L297" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="B298" t="n">
+        <v>71.759</v>
+      </c>
+      <c r="L298" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="B299" t="n">
+        <v>71.446</v>
+      </c>
+      <c r="L299" t="n">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>78</v>
+      </c>
+      <c r="B300" t="n">
+        <v>70.78400000000001</v>
+      </c>
+      <c r="L300" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="B301" t="n">
+        <v>70.61</v>
+      </c>
+      <c r="L301" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="B302" t="n">
+        <v>69.78099999999999</v>
+      </c>
+      <c r="L302" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="B303" t="n">
+        <v>69.482</v>
+      </c>
+      <c r="L303" t="n">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>79</v>
+      </c>
+      <c r="B304" t="n">
+        <v>69.07599999999999</v>
+      </c>
+      <c r="L304" t="n">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="B305" t="n">
+        <v>68.122</v>
+      </c>
+      <c r="L305" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="B306" t="n">
+        <v>66.81100000000001</v>
+      </c>
+      <c r="L306" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="B307" t="n">
+        <v>66.724</v>
+      </c>
+      <c r="L307" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>80</v>
+      </c>
+      <c r="B308" t="n">
+        <v>66.515</v>
+      </c>
+      <c r="L308" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="B309" t="n">
+        <v>66.502</v>
+      </c>
+      <c r="L309" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="B310" t="n">
+        <v>66.441</v>
+      </c>
+      <c r="L310" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="B311" t="n">
+        <v>66.892</v>
+      </c>
+      <c r="L311" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>81</v>
+      </c>
+      <c r="B312" t="n">
+        <v>66.628</v>
+      </c>
+      <c r="L312" t="n">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="B313" t="n">
+        <v>65.721</v>
+      </c>
+      <c r="L313" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="B314" t="n">
+        <v>65.06399999999999</v>
+      </c>
+      <c r="L314" t="n">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="B315" t="n">
+        <v>64.955</v>
+      </c>
+      <c r="L315" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>82</v>
+      </c>
+      <c r="B316" t="n">
+        <v>64.44900000000001</v>
+      </c>
+      <c r="L316" t="n">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="B317" t="n">
+        <v>64.91500000000001</v>
+      </c>
+      <c r="L317" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="B318" t="n">
+        <v>66.078</v>
+      </c>
+      <c r="L318" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="B319" t="n">
+        <v>66.815</v>
+      </c>
+      <c r="L319" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>83</v>
+      </c>
+      <c r="B320" t="n">
+        <v>67.66800000000001</v>
+      </c>
+      <c r="L320" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="B321" t="n">
+        <v>68.95699999999999</v>
+      </c>
+      <c r="L321" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="B322" t="n">
+        <v>68.974</v>
+      </c>
+      <c r="L322" t="n">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="B323" t="n">
+        <v>68.518</v>
+      </c>
+      <c r="L323" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>84</v>
+      </c>
+      <c r="B324" t="n">
+        <v>68.502</v>
+      </c>
+      <c r="L324" t="n">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="B325" t="n">
+        <v>68.23399999999999</v>
+      </c>
+      <c r="L325" t="n">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="B326" t="n">
+        <v>67.82299999999999</v>
+      </c>
+      <c r="L326" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="B327" t="n">
+        <v>68.73699999999999</v>
+      </c>
+      <c r="L327" t="n">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>85</v>
+      </c>
+      <c r="B328" t="n">
+        <v>69.901</v>
+      </c>
+      <c r="L328" t="n">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="B329" t="n">
+        <v>70.503</v>
+      </c>
+      <c r="L329" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="B330" t="n">
+        <v>71.03399999999999</v>
+      </c>
+      <c r="L330" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="B331" t="n">
+        <v>71.58</v>
+      </c>
+      <c r="L331" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>86</v>
+      </c>
+      <c r="B332" t="n">
+        <v>71.551</v>
+      </c>
+      <c r="L332" t="n">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="B333" t="n">
+        <v>70.229</v>
+      </c>
+      <c r="L333" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="B334" t="n">
+        <v>67.845</v>
+      </c>
+      <c r="L334" t="n">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="B335" t="n">
+        <v>65.15299999999999</v>
+      </c>
+      <c r="L335" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>87</v>
+      </c>
+      <c r="B336" t="n">
+        <v>63.227</v>
+      </c>
+      <c r="L336" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="B337" t="n">
+        <v>61.91800000000001</v>
+      </c>
+      <c r="L337" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="B338" t="n">
+        <v>61.286</v>
+      </c>
+      <c r="L338" t="n">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="B339" t="n">
+        <v>62.51900000000001</v>
+      </c>
+      <c r="L339" t="n">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>88</v>
+      </c>
+      <c r="B340" t="n">
+        <v>65.19033333333333</v>
+      </c>
+      <c r="L340" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="B341" t="n">
+        <v>67.05600000000001</v>
+      </c>
+      <c r="L341" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="B342" t="n">
+        <v>68.25200000000001</v>
+      </c>
+      <c r="L342" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="B343" t="n">
+        <v>69.96000000000001</v>
+      </c>
+      <c r="L343" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>89</v>
+      </c>
+      <c r="B344" t="n">
+        <v>71.348</v>
+      </c>
+      <c r="L344" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="B345" t="n">
+        <v>71.71666666666665</v>
+      </c>
+      <c r="L345" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="B346" t="n">
+        <v>71.72199999999999</v>
+      </c>
+      <c r="L346" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="B347" t="n">
+        <v>71.86899999999999</v>
+      </c>
+      <c r="L347" t="n">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>90</v>
+      </c>
+      <c r="B348" t="n">
+        <v>72.35599999999999</v>
+      </c>
+      <c r="L348" t="n">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="B349" t="n">
+        <v>72.768</v>
+      </c>
+      <c r="L349" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="B350" t="n">
+        <v>73.42100000000001</v>
+      </c>
+      <c r="L350" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="B351" t="n">
+        <v>74.47900000000001</v>
+      </c>
+      <c r="L351" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>91</v>
+      </c>
+      <c r="B352" t="n">
+        <v>75.17133333333334</v>
+      </c>
+      <c r="L352" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="B353" t="n">
+        <v>75.378</v>
+      </c>
+      <c r="L353" t="n">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="B354" t="n">
+        <v>75.333</v>
+      </c>
+      <c r="L354" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="B355" t="n">
+        <v>75.248</v>
+      </c>
+      <c r="L355" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>92</v>
+      </c>
+      <c r="B356" t="n">
+        <v>74.914</v>
+      </c>
+      <c r="L356" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="B357" t="n">
+        <v>74.39966666666666</v>
+      </c>
+      <c r="L357" t="n">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="B358" t="n">
+        <v>73.38800000000001</v>
+      </c>
+      <c r="L358" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="B359" t="n">
+        <v>72.68299999999999</v>
+      </c>
+      <c r="L359" t="n">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>93</v>
+      </c>
+      <c r="B360" t="n">
+        <v>72.13699999999999</v>
+      </c>
+      <c r="L360" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="B361" t="n">
+        <v>71.262</v>
+      </c>
+      <c r="L361" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="B362" t="n">
+        <v>71.062</v>
+      </c>
+      <c r="L362" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="B363" t="n">
+        <v>71.337</v>
+      </c>
+      <c r="L363" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>94</v>
+      </c>
+      <c r="B364" t="n">
+        <v>71.056</v>
+      </c>
+      <c r="L364" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="B365" t="n">
+        <v>70.825</v>
+      </c>
+      <c r="L365" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="B366" t="n">
+        <v>70.86199999999999</v>
+      </c>
+      <c r="L366" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="B367" t="n">
+        <v>70.36699999999999</v>
+      </c>
+      <c r="L367" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>95</v>
+      </c>
+      <c r="B368" t="n">
+        <v>70.28566666666666</v>
+      </c>
+      <c r="L368" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="B369" t="n">
+        <v>70.761</v>
+      </c>
+      <c r="L369" t="n">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="B370" t="n">
+        <v>71.304</v>
+      </c>
+      <c r="L370" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="B371" t="n">
+        <v>71.67400000000001</v>
+      </c>
+      <c r="L371" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>96</v>
+      </c>
+      <c r="B372" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="L372" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="B373" t="n">
+        <v>71.12933333333334</v>
+      </c>
+      <c r="L373" t="n">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="B374" t="n">
+        <v>70.19199999999999</v>
+      </c>
+      <c r="L374" t="n">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="B375" t="n">
+        <v>69.024</v>
+      </c>
+      <c r="L375" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>97</v>
+      </c>
+      <c r="B376" t="n">
+        <v>68.46299999999999</v>
+      </c>
+      <c r="L376" t="n">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="B377" t="n">
+        <v>68.14500000000001</v>
+      </c>
+      <c r="L377" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="B378" t="n">
+        <v>67.777</v>
+      </c>
+      <c r="L378" t="n">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="B379" t="n">
+        <v>67.657</v>
+      </c>
+      <c r="L379" t="n">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>98</v>
+      </c>
+      <c r="B380" t="n">
+        <v>67.37299999999999</v>
+      </c>
+      <c r="L380" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="B381" t="n">
+        <v>66.652</v>
+      </c>
+      <c r="L381" t="n">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="B382" t="n">
+        <v>65.947</v>
+      </c>
+      <c r="L382" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="B383" t="n">
+        <v>65.20466666666667</v>
+      </c>
+      <c r="L383" t="n">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>99</v>
+      </c>
+      <c r="B384" t="n">
+        <v>64.372</v>
+      </c>
+      <c r="L384" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="B385" t="n">
+        <v>63.76600000000001</v>
+      </c>
+      <c r="L385" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="B386" t="n">
+        <v>63.53400000000001</v>
+      </c>
+      <c r="L386" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="B387" t="n">
+        <v>63.888</v>
+      </c>
+      <c r="L387" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>100</v>
+      </c>
+      <c r="B388" t="n">
+        <v>65.03933333333333</v>
+      </c>
+      <c r="L388" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="B389" t="n">
+        <v>66.167</v>
+      </c>
+      <c r="L389" t="n">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="B390" t="n">
+        <v>66.95099999999999</v>
+      </c>
+      <c r="L390" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="B391" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="L391" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>101</v>
+      </c>
+      <c r="B392" t="n">
+        <v>67.33500000000001</v>
+      </c>
+      <c r="L392" t="n">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="B393" t="n">
+        <v>67.158</v>
+      </c>
+      <c r="L393" t="n">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="B394" t="n">
+        <v>67.377</v>
+      </c>
+      <c r="L394" t="n">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="B395" t="n">
+        <v>67.96700000000001</v>
+      </c>
+      <c r="L395" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>102</v>
+      </c>
+      <c r="B396" t="n">
+        <v>68.399</v>
+      </c>
+      <c r="L396" t="n">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="B397" t="n">
+        <v>68.816</v>
+      </c>
+      <c r="L397" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="B398" t="n">
+        <v>69.069</v>
+      </c>
+      <c r="L398" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="B399" t="n">
+        <v>69.22233333333334</v>
+      </c>
+      <c r="L399" t="n">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>103</v>
+      </c>
+      <c r="B400" t="n">
+        <v>69.17700000000001</v>
+      </c>
+      <c r="L400" t="n">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="B401" t="n">
+        <v>69.477</v>
+      </c>
+      <c r="L401" t="n">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B402" t="n">
+        <v>70.26366666666667</v>
+      </c>
+      <c r="L402" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="B403" t="n">
+        <v>70.96900000000001</v>
+      </c>
+      <c r="L403" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>104</v>
+      </c>
+      <c r="B404" t="n">
+        <v>71.69566666666667</v>
+      </c>
+      <c r="L404" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="B405" t="n">
+        <v>72.24433333333334</v>
+      </c>
+      <c r="L405" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="B406" t="n">
+        <v>72.41799999999999</v>
+      </c>
+      <c r="L406" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="B407" t="n">
+        <v>72.304</v>
+      </c>
+      <c r="L407" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>105</v>
+      </c>
+      <c r="B408" t="n">
+        <v>72.342</v>
+      </c>
+      <c r="L408" t="n">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="B409" t="n">
+        <v>72.899</v>
+      </c>
+      <c r="L409" t="n">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="B410" t="n">
+        <v>73.78966666666665</v>
+      </c>
+      <c r="L410" t="n">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="B411" t="n">
+        <v>74.64699999999999</v>
+      </c>
+      <c r="L411" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>106</v>
+      </c>
+      <c r="B412" t="n">
+        <v>75.477</v>
+      </c>
+      <c r="L412" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="B413" t="n">
+        <v>76.313</v>
+      </c>
+      <c r="L413" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="B414" t="n">
+        <v>76.828</v>
+      </c>
+      <c r="L414" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="B415" t="n">
+        <v>77.36666666666666</v>
+      </c>
+      <c r="L415" t="n">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>107</v>
+      </c>
+      <c r="B416" t="n">
+        <v>78.256</v>
+      </c>
+      <c r="L416" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="B417" t="n">
+        <v>79.05333333333333</v>
+      </c>
+      <c r="L417" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="B418" t="n">
+        <v>79.42866666666666</v>
+      </c>
+      <c r="L418" t="n">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="B419" t="n">
+        <v>79.422</v>
+      </c>
+      <c r="L419" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>108</v>
+      </c>
+      <c r="B420" t="n">
+        <v>78.88266666666667</v>
+      </c>
+      <c r="L420" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="B421" t="n">
+        <v>77.86799999999999</v>
+      </c>
+      <c r="L421" t="n">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="B422" t="n">
+        <v>77.151</v>
+      </c>
+      <c r="L422" t="n">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="B423" t="n">
+        <v>77.22366666666667</v>
+      </c>
+      <c r="L423" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>109</v>
+      </c>
+      <c r="B424" t="n">
+        <v>77.31299999999999</v>
+      </c>
+      <c r="L424" t="n">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="B425" t="n">
+        <v>77.85666666666665</v>
+      </c>
+      <c r="L425" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="B426" t="n">
+        <v>78.89333333333335</v>
+      </c>
+      <c r="L426" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="B427" t="n">
+        <v>79.76899999999999</v>
+      </c>
+      <c r="L427" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>110</v>
+      </c>
+      <c r="B428" t="n">
+        <v>80.03566666666667</v>
+      </c>
+      <c r="L428" t="n">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="B429" t="n">
+        <v>80.29299999999999</v>
+      </c>
+      <c r="L429" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="B430" t="n">
+        <v>80.52200000000001</v>
+      </c>
+      <c r="L430" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="B431" t="n">
+        <v>80.46466666666666</v>
+      </c>
+      <c r="L431" t="n">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>111</v>
+      </c>
+      <c r="B432" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="L432" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="B433" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="L433" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="B434" t="n">
+        <v>78.87199999999999</v>
+      </c>
+      <c r="L434" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="B435" t="n">
+        <v>78.21599999999999</v>
+      </c>
+      <c r="L435" t="n">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>112</v>
+      </c>
+      <c r="B436" t="n">
+        <v>77.94666666666667</v>
+      </c>
+      <c r="L436" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="B437" t="n">
+        <v>78.04400000000001</v>
+      </c>
+      <c r="L437" t="n">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B438" t="n">
+        <v>78.42100000000001</v>
+      </c>
+      <c r="L438" t="n">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="B439" t="n">
+        <v>78.71099999999998</v>
+      </c>
+      <c r="L439" t="n">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>113</v>
+      </c>
+      <c r="B440" t="n">
+        <v>78.91400000000002</v>
+      </c>
+      <c r="L440" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="B441" t="n">
+        <v>78.69866666666667</v>
+      </c>
+      <c r="L441" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="B442" t="n">
+        <v>78.152</v>
+      </c>
+      <c r="L442" t="n">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="B443" t="n">
+        <v>77.32300000000001</v>
+      </c>
+      <c r="L443" t="n">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>114</v>
+      </c>
+      <c r="B444" t="n">
+        <v>76.54299999999999</v>
+      </c>
+      <c r="L444" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="B445" t="n">
+        <v>75.812</v>
+      </c>
+      <c r="L445" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="B446" t="n">
+        <v>75.30666666666667</v>
+      </c>
+      <c r="L446" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="B447" t="n">
+        <v>74.94</v>
+      </c>
+      <c r="L447" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>115</v>
+      </c>
+      <c r="B448" t="n">
+        <v>74.65049999999999</v>
+      </c>
+      <c r="L448" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="B449" t="n">
+        <v>74.29949999999999</v>
+      </c>
+      <c r="L449" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="B450" t="n">
+        <v>73.887</v>
+      </c>
+      <c r="L450" t="n">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="B451" t="n">
+        <v>73.4755</v>
+      </c>
+      <c r="L451" t="n">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>116</v>
+      </c>
+      <c r="B452" t="n">
+        <v>73.1645</v>
+      </c>
+      <c r="L452" t="n">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="B453" t="n">
+        <v>73.0535</v>
+      </c>
+      <c r="L453" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="B454" t="n">
+        <v>73.03783333333334</v>
+      </c>
+      <c r="L454" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="B455" t="n">
+        <v>73.05499999999999</v>
+      </c>
+      <c r="L455" t="n">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>117</v>
+      </c>
+      <c r="B456" t="n">
+        <v>73.04249999999999</v>
+      </c>
+      <c r="L456" t="n">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="B457" t="n">
+        <v>72.90083333333334</v>
+      </c>
+      <c r="L457" t="n">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="B458" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="L458" t="n">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="B459" t="n">
+        <v>72.34966666666665</v>
+      </c>
+      <c r="L459" t="n">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>118</v>
+      </c>
+      <c r="B460" t="n">
+        <v>72.18899999999999</v>
+      </c>
+      <c r="L460" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="B461" t="n">
+        <v>72.148</v>
+      </c>
+      <c r="L461" t="n">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="B462" t="n">
+        <v>72.22666666666666</v>
+      </c>
+      <c r="L462" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="B463" t="n">
+        <v>72.425</v>
+      </c>
+      <c r="L463" t="n">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>119</v>
+      </c>
+      <c r="B464" t="n">
+        <v>72.66433333333332</v>
+      </c>
+      <c r="L464" t="n">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="B465" t="n">
+        <v>72.825</v>
+      </c>
+      <c r="L465" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="B466" t="n">
+        <v>72.907</v>
+      </c>
+      <c r="L466" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="B467" t="n">
+        <v>72.91033333333334</v>
+      </c>
+      <c r="L467" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>120</v>
+      </c>
+      <c r="B468" t="n">
+        <v>72.83500000000001</v>
+      </c>
+      <c r="L468" t="n">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="B469" t="n">
+        <v>72.69933333333333</v>
+      </c>
+      <c r="L469" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="B470" t="n">
+        <v>72.58200000000001</v>
+      </c>
+      <c r="L470" t="n">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="B471" t="n">
+        <v>72.48299999999999</v>
+      </c>
+      <c r="L471" t="n">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>121</v>
+      </c>
+      <c r="B472" t="n">
+        <v>72.40233333333335</v>
+      </c>
+      <c r="L472" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="B473" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="L473" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B474" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="L474" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="B475" t="n">
+        <v>72.264</v>
+      </c>
+      <c r="L475" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>122</v>
+      </c>
+      <c r="B476" t="n">
+        <v>72.232</v>
+      </c>
+      <c r="L476" t="n">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="B477" t="n">
+        <v>72.20399999999999</v>
+      </c>
+      <c r="L477" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="B478" t="n">
+        <v>72.17999999999999</v>
+      </c>
+      <c r="L478" t="n">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="B479" t="n">
+        <v>72.13066666666666</v>
+      </c>
+      <c r="L479" t="n">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>123</v>
+      </c>
+      <c r="B480" t="n">
+        <v>72.05200000000001</v>
+      </c>
+      <c r="L480" t="n">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="B481" t="n">
+        <v>71.94399999999999</v>
+      </c>
+      <c r="L481" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="B482" t="n">
+        <v>71.80666666666667</v>
+      </c>
+      <c r="L482" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="B483" t="n">
+        <v>71.64</v>
+      </c>
+      <c r="L483" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>124</v>
+      </c>
+      <c r="B484" t="n">
+        <v>71.376</v>
+      </c>
+      <c r="L484" t="n">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="B485" t="n">
+        <v>71.04400000000001</v>
+      </c>
+      <c r="L485" t="n">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="B486" t="n">
+        <v>70.64400000000001</v>
+      </c>
+      <c r="L486" t="n">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="B487" t="n">
+        <v>70.176</v>
+      </c>
+      <c r="L487" t="n">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>125</v>
+      </c>
+      <c r="B488" t="n">
+        <v>69.64</v>
+      </c>
+      <c r="L488" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="B489" t="n">
+        <v>68.97433333333333</v>
+      </c>
+      <c r="L489" t="n">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="B490" t="n">
+        <v>68.247</v>
+      </c>
+      <c r="L490" t="n">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="B491" t="n">
+        <v>67.458</v>
+      </c>
+      <c r="L491" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>126</v>
+      </c>
+      <c r="B492" t="n">
+        <v>66.60733333333333</v>
+      </c>
+      <c r="L492" t="n">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="B493" t="n">
+        <v>65.69499999999999</v>
+      </c>
+      <c r="L493" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="B494" t="n">
+        <v>65.32693333333333</v>
+      </c>
+      <c r="L494" t="n">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="B495" t="n">
+        <v>65.56479999999999</v>
+      </c>
+      <c r="L495" t="n">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>127</v>
+      </c>
+      <c r="B496" t="n">
+        <v>66.40860000000001</v>
+      </c>
+      <c r="L496" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="B497" t="n">
+        <v>67.85833333333333</v>
+      </c>
+      <c r="L497" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="B498" t="n">
+        <v>69.857</v>
+      </c>
+      <c r="L498" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="B499" t="n">
+        <v>71.51739999999999</v>
+      </c>
+      <c r="L499" t="n">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>128</v>
+      </c>
+      <c r="B500" t="n">
+        <v>72.6772</v>
+      </c>
+      <c r="L500" t="n">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="B501" t="n">
+        <v>73.3364</v>
+      </c>
+      <c r="L501" t="n">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="B502" t="n">
+        <v>73.495</v>
+      </c>
+      <c r="L502" t="n">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="B503" t="n">
+        <v>73.21639999999999</v>
+      </c>
+      <c r="L503" t="n">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>129</v>
+      </c>
+      <c r="B504" t="n">
+        <v>73.00120000000001</v>
+      </c>
+      <c r="L504" t="n">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="B505" t="n">
+        <v>72.84939999999999</v>
+      </c>
+      <c r="L505" t="n">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="B506" t="n">
+        <v>72.761</v>
+      </c>
+      <c r="L506" t="n">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="B507" t="n">
+        <v>71.93600000000001</v>
+      </c>
+      <c r="L507" t="n">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>130</v>
+      </c>
+      <c r="B508" t="n">
+        <v>70.3616</v>
+      </c>
+      <c r="L508" t="n">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="B509" t="n">
+        <v>68.34613333333334</v>
+      </c>
+      <c r="L509" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B510" t="n">
+        <v>66.6896</v>
+      </c>
+      <c r="L510" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="B511" t="n">
+        <v>65.39200000000001</v>
+      </c>
+      <c r="L511" t="n">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>131</v>
+      </c>
+      <c r="B512" t="n">
+        <v>64.88799999999999</v>
+      </c>
+      <c r="L512" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="B513" t="n">
+        <v>65.29133333333333</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="B514" t="n">
+        <v>66.23666666666668</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="B515" t="n">
+        <v>66.12666666666667</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>132</v>
+      </c>
+      <c r="B516" t="n">
+        <v>64.85400000000001</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="B517" t="n">
+        <v>63.55866666666667</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="B518" t="n">
+        <v>62.93066666666666</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="B519" t="n">
+        <v>63.33</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>133</v>
+      </c>
+      <c r="B520" t="n">
+        <v>64.77933333333333</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="B521" t="n">
+        <v>67.20933333333333</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="B522" t="n">
+        <v>69.48533333333333</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="B523" t="n">
+        <v>70.8095</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>134</v>
+      </c>
+      <c r="B524" t="n">
+        <v>70.99850000000001</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="B525" t="n">
+        <v>70.82700000000001</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="B526" t="n">
+        <v>70.17666666666668</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>134.75</v>
+      </c>
+      <c r="B527" t="n">
+        <v>69.40799999999999</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>135</v>
+      </c>
+      <c r="B528" t="n">
+        <v>68.5215</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="B529" t="n">
+        <v>67.4225</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="B530" t="n">
+        <v>66.40599999999999</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>135.75</v>
+      </c>
+      <c r="B531" t="n">
+        <v>65.76700000000001</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>136</v>
+      </c>
+      <c r="B532" t="n">
+        <v>65.7855</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="B533" t="n">
+        <v>66.37950000000001</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="B534" t="n">
+        <v>67.46700000000001</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>136.75</v>
+      </c>
+      <c r="B535" t="n">
+        <v>68.76599999999999</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>137</v>
+      </c>
+      <c r="B536" t="n">
+        <v>69.99600000000001</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="B537" t="n">
+        <v>70.87650000000001</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="B538" t="n">
+        <v>71.63200000000001</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="B539" t="n">
+        <v>72.2495</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>138</v>
+      </c>
+      <c r="B540" t="n">
+        <v>72.71600000000001</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>138.25</v>
+      </c>
+      <c r="B541" t="n">
+        <v>73.35900000000001</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="B542" t="n">
+        <v>74.03599999999999</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>138.75</v>
+      </c>
+      <c r="B543" t="n">
+        <v>74.6045</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>139</v>
+      </c>
+      <c r="B544" t="n">
+        <v>74.96483333333333</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>139.25</v>
+      </c>
+      <c r="B545" t="n">
+        <v>75.06999999999999</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B546" t="n">
+        <v>75.01600000000001</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>139.75</v>
+      </c>
+      <c r="B547" t="n">
+        <v>75.05800000000001</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>140</v>
+      </c>
+      <c r="B548" t="n">
+        <v>75.196</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="B549" t="n">
+        <v>75.69616666666667</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="B550" t="n">
+        <v>76.46250000000001</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>140.75</v>
+      </c>
+      <c r="B551" t="n">
+        <v>77.352</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>141</v>
+      </c>
+      <c r="B552" t="n">
+        <v>78.21771428571428</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>141.25</v>
+      </c>
+      <c r="B553" t="n">
+        <v>78.90614285714285</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="B554" t="n">
+        <v>79.26378571428572</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="B555" t="n">
+        <v>79.43364285714286</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>142</v>
+      </c>
+      <c r="B556" t="n">
+        <v>79.41571428571429</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="B557" t="n">
+        <v>79.24428571428572</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="B558" t="n">
+        <v>78.79935714285715</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="B559" t="n">
+        <v>78.1152142857143</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>143</v>
+      </c>
+      <c r="B560" t="n">
+        <v>77.19185714285715</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="B561" t="n">
+        <v>75.86578571428572</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="B562" t="n">
+        <v>74.4105</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>143.75</v>
+      </c>
+      <c r="B563" t="n">
+        <v>73.09950000000001</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>144</v>
+      </c>
+      <c r="B564" t="n">
+        <v>72.23699999999999</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="B565" t="n">
+        <v>71.98650000000001</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="B566" t="n">
+        <v>72.5115</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="B567" t="n">
+        <v>73.47750000000001</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>145</v>
+      </c>
+      <c r="B568" t="n">
+        <v>74.54600000000001</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>145.25</v>
+      </c>
+      <c r="B569" t="n">
+        <v>75.3785</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="B570" t="n">
+        <v>75.86816666666667</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="B571" t="n">
+        <v>76.07600000000001</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>146</v>
+      </c>
+      <c r="B572" t="n">
+        <v>75.91500000000001</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="B573" t="n">
+        <v>75.667</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="B574" t="n">
+        <v>75.33200000000001</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>146.75</v>
+      </c>
+      <c r="B575" t="n">
+        <v>74.76433333333333</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>147</v>
+      </c>
+      <c r="B576" t="n">
+        <v>74.05100000000002</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>147.25</v>
+      </c>
+      <c r="B577" t="n">
+        <v>73.34</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="B578" t="n">
+        <v>72.76000000000002</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="B579" t="n">
+        <v>72.40000000000001</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>148</v>
+      </c>
+      <c r="B580" t="n">
+        <v>72.349</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>148.25</v>
+      </c>
+      <c r="B581" t="n">
+        <v>72.4325</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="B582" t="n">
+        <v>72.57849999999999</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>148.75</v>
+      </c>
+      <c r="B583" t="n">
+        <v>72.715</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>149</v>
+      </c>
+      <c r="B584" t="n">
+        <v>72.771</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>149.25</v>
+      </c>
+      <c r="B585" t="n">
+        <v>72.773</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="B586" t="n">
+        <v>72.7475</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>149.75</v>
+      </c>
+      <c r="B587" t="n">
+        <v>72.726</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>150</v>
+      </c>
+      <c r="B588" t="n">
+        <v>72.6905</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="B589" t="n">
+        <v>72.623</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="B590" t="n">
+        <v>72.6845</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>150.75</v>
+      </c>
+      <c r="B591" t="n">
+        <v>72.91550000000001</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>151</v>
+      </c>
+      <c r="B592" t="n">
+        <v>73.35650000000001</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="B593" t="n">
+        <v>74.09883333333335</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="B594" t="n">
+        <v>74.955</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="B595" t="n">
+        <v>75.86999999999999</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>152</v>
+      </c>
+      <c r="B596" t="n">
+        <v>76.72999999999999</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>152.25</v>
+      </c>
+      <c r="B597" t="n">
+        <v>77.535</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="B598" t="n">
+        <v>78.07816666666666</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>152.75</v>
+      </c>
+      <c r="B599" t="n">
+        <v>78.4145</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>153</v>
+      </c>
+      <c r="B600" t="n">
+        <v>78.4115</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>153.25</v>
+      </c>
+      <c r="B601" t="n">
+        <v>78.25749999999999</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="B602" t="n">
+        <v>78.08599999999998</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>153.75</v>
+      </c>
+      <c r="B603" t="n">
+        <v>78.03049999999999</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>154</v>
+      </c>
+      <c r="B604" t="n">
+        <v>78.08199999999999</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="B605" t="n">
+        <v>78.1255</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="B606" t="n">
+        <v>78.04599999999999</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="B607" t="n">
+        <v>77.499</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>155</v>
+      </c>
+      <c r="B608" t="n">
+        <v>76.62599999999999</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>155.25</v>
+      </c>
+      <c r="B609" t="n">
+        <v>75.5685</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="B610" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="B611" t="n">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -58427,7 +65043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58501,6 +65117,88 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>SAMPLING &lt;i&gt;&lt;b&gt;Id-B18F0F5A&lt;/i&gt;&lt;/b&gt; with parameters :&lt;ul&gt;&lt;li&gt;Step : 0.25&lt;li&gt;Kind of interpolation : linear&lt;li&gt;Integrated : False&lt;/ul&gt;</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="91" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FILTER</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Moving average 5 pts</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/30 at 15:02:08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FILTER &lt;i&gt;&lt;b&gt;Id-D87F3640&lt;/i&gt;&lt;/b&gt; with parameters :&lt;ul&gt;&lt;li&gt;Moving average size : 5&lt;/ul&gt;</t>
         </is>
       </c>
     </row>

--- a/EGU26/GeoB4411-2_EGU26.xlsx
+++ b/EGU26/GeoB4411-2_EGU26.xlsx
@@ -27,10 +27,11 @@
     <sheet name="Series Id-1E1D79CD" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Series Id-D6812469" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Series Id-2DD42753" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Series Id-CB45AB6E" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="INTERPOLATION Id-F0BB8C98" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="SAMPLING Id-B18F0F5A" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="FILTER Id-D87F3640" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Series Id-5CCCECF3" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Series Id-CB45AB6E" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="INTERPOLATION Id-F0BB8C98" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="SAMPLING Id-B18F0F5A" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="FILTER Id-D87F3640" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +469,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saved 2026/04/30 at 16:41:00</t>
+          <t>Saved 2026/04/30 at 17:55:16</t>
         </is>
       </c>
     </row>
@@ -58231,6 +58232,4978 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H611"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="57" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="489" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>MD2042_AgeAICC2012_d18OBtq_ka</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>GeoB4411_PercAndes</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="B2" t="n">
+        <v>73.18265321202342</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Series freq. filtered</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Butterworth | period band | P=[18.0, 25.0] | order=4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>#2ca02c</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Created 2026/04/30 17:52:55</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Imported series&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-1E1D79CD&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-1E1D79CD&lt;/i&gt;&lt;/b&gt; interpolated with INTERPOLATION &lt;i&gt;&lt;b&gt;Id-F0BB8C98&lt;/i&gt;&lt;/b&gt; with mode Linear&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-D6812469&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Series &lt;i&gt;&lt;b&gt;Id-D6812469&lt;/i&gt;&lt;/b&gt; sampled every 0.25 and linear interpolation with SAMPLING &lt;i&gt;&lt;b&gt;Id-B18F0F5A&lt;/i&gt;&lt;/b&gt;&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-2DD42753&lt;/b&gt;&lt;/i&gt;&lt;li&gt;Frequency filter: Butterworth | period band | P=[18.0, 25.0] | order=4&lt;BR&gt;---&gt; series &lt;i&gt;&lt;b&gt;Id-5CCCECF3&lt;/b&gt;&lt;/i&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="B3" t="n">
+        <v>73.15366914698727</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>73.11660728155582</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="B5" t="n">
+        <v>73.07158483774467</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>73.01876339680231</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="B7" t="n">
+        <v>72.95834837072653</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="n">
+        <v>72.89058822489042</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="B9" t="n">
+        <v>72.81577345472783</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="B10" t="n">
+        <v>72.73423532085596</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="B11" t="n">
+        <v>72.64634434842067</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="n">
+        <v>72.55250859782814</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="B13" t="n">
+        <v>72.45317171536632</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>72.34881077351461</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="B15" t="n">
+        <v>72.23993391198114</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" t="n">
+        <v>72.12707779168835</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="B17" t="n">
+        <v>72.01080487504049</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>71.89170054684591</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="B19" t="n">
+        <v>71.77037009122539</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B20" t="n">
+        <v>71.64743554071069</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="B21" t="n">
+        <v>71.52353241451789</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="B22" t="n">
+        <v>71.39930636366579</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="B23" t="n">
+        <v>71.27540974119378</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" t="n">
+        <v>71.15249811621545</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="B25" t="n">
+        <v>71.03122675091886</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="B26" t="n">
+        <v>70.91224705989134</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="B27" t="n">
+        <v>70.7962030713031</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" t="n">
+        <v>70.68372790952986</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="B29" t="n">
+        <v>70.57544031872837</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B30" t="n">
+        <v>70.47194124670159</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="B31" t="n">
+        <v>70.37381050810365</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" t="n">
+        <v>70.28160354563865</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="B33" t="n">
+        <v>70.19584830740671</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="B34" t="n">
+        <v>70.11704225794672</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="B35" t="n">
+        <v>70.0456495398217</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>12</v>
+      </c>
+      <c r="B36" t="n">
+        <v>69.98209830179464</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="B37" t="n">
+        <v>69.92677820875382</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="B38" t="n">
+        <v>69.88003814757226</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="B39" t="n">
+        <v>69.84218414203215</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>69.81347748881805</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.79413312538827</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B42" t="n">
+        <v>69.78431823927951</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="B43" t="n">
+        <v>69.7841511270927</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" t="n">
+        <v>69.79370031005453</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="B45" t="n">
+        <v>69.81298391165909</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="B46" t="n">
+        <v>69.84196930147229</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="B47" t="n">
+        <v>69.88057300773926</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>15</v>
+      </c>
+      <c r="B48" t="n">
+        <v>69.92866089997803</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="B49" t="n">
+        <v>69.98604864128014</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="B50" t="n">
+        <v>70.05250240857856</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="B51" t="n">
+        <v>70.12773987769428</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B52" t="n">
+        <v>70.21143146854145</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="B53" t="n">
+        <v>70.30320184446738</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>70.40263165833301</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="B55" t="n">
+        <v>70.50925953661111</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>17</v>
+      </c>
+      <c r="B56" t="n">
+        <v>70.62258429149976</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="B57" t="n">
+        <v>70.74206734982397</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="B58" t="n">
+        <v>70.86713538633659</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="B59" t="n">
+        <v>70.99718314793537</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>18</v>
+      </c>
+      <c r="B60" t="n">
+        <v>71.13157645429335</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="B61" t="n">
+        <v>71.26965535945835</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="B62" t="n">
+        <v>71.41073745812061</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="B63" t="n">
+        <v>71.55412131947844</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>19</v>
+      </c>
+      <c r="B64" t="n">
+        <v>71.69909003095485</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="B65" t="n">
+        <v>71.84491483343677</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="B66" t="n">
+        <v>71.99085882922493</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="B67" t="n">
+        <v>72.13618074349922</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20</v>
+      </c>
+      <c r="B68" t="n">
+        <v>72.2801387198227</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="B69" t="n">
+        <v>72.42199413002909</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="B70" t="n">
+        <v>72.56101537876511</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="B71" t="n">
+        <v>72.69648168298814</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>21</v>
+      </c>
+      <c r="B72" t="n">
+        <v>72.82768680685415</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="B73" t="n">
+        <v>72.9539427326649</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="B74" t="n">
+        <v>73.07458324887934</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="B75" t="n">
+        <v>73.18896743662607</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>22</v>
+      </c>
+      <c r="B76" t="n">
+        <v>73.29648303668243</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="B77" t="n">
+        <v>73.39654967950439</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="B78" t="n">
+        <v>73.48862196159966</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="B79" t="n">
+        <v>73.57219235232785</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>23</v>
+      </c>
+      <c r="B80" t="n">
+        <v>73.64679391608236</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="B81" t="n">
+        <v>73.71200283575477</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="B82" t="n">
+        <v>73.76744072439676</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="B83" t="n">
+        <v>73.81277671307387</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>24</v>
+      </c>
+      <c r="B84" t="n">
+        <v>73.84772930404162</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="B85" t="n">
+        <v>73.87206797956303</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="B86" t="n">
+        <v>73.88561455792076</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="B87" t="n">
+        <v>73.88824428944987</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>25</v>
+      </c>
+      <c r="B88" t="n">
+        <v>73.87988668672331</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="B89" t="n">
+        <v>73.86052608435317</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="B90" t="n">
+        <v>73.83020192522132</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="B91" t="n">
+        <v>73.78900877131564</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>26</v>
+      </c>
+      <c r="B92" t="n">
+        <v>73.7370960387161</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="B93" t="n">
+        <v>73.67466745764162</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="B94" t="n">
+        <v>73.60198025982832</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="B95" t="n">
+        <v>73.5193440968539</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>27</v>
+      </c>
+      <c r="B96" t="n">
+        <v>73.42711969434706</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="B97" t="n">
+        <v>73.3257172483177</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="B98" t="n">
+        <v>73.21559457110668</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="B99" t="n">
+        <v>73.09725499567864</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>28</v>
+      </c>
+      <c r="B100" t="n">
+        <v>72.97124504816098</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="B101" t="n">
+        <v>72.83815189966134</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="B102" t="n">
+        <v>72.69860060947111</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="B103" t="n">
+        <v>72.55325117277641</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>29</v>
+      </c>
+      <c r="B104" t="n">
+        <v>72.40279538694902</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="B105" t="n">
+        <v>72.24795355137095</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="B106" t="n">
+        <v>72.08947101655704</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="B107" t="n">
+        <v>71.92811459907345</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>30</v>
+      </c>
+      <c r="B108" t="n">
+        <v>71.7646688794072</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="B109" t="n">
+        <v>71.59993240051561</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="B110" t="n">
+        <v>71.4347137852773</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>30.75</v>
+      </c>
+      <c r="B111" t="n">
+        <v>71.26982779147107</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>31</v>
+      </c>
+      <c r="B112" t="n">
+        <v>71.10609132322942</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="B113" t="n">
+        <v>70.94431941814254</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="B114" t="n">
+        <v>70.78532122933171</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="B115" t="n">
+        <v>70.62989602186232</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>32</v>
+      </c>
+      <c r="B116" t="n">
+        <v>70.47882920282981</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="B117" t="n">
+        <v>70.3328884043264</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="B118" t="n">
+        <v>70.19281963828188</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="B119" t="n">
+        <v>70.05934354187133</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>33</v>
+      </c>
+      <c r="B120" t="n">
+        <v>69.93315173179531</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="B121" t="n">
+        <v>69.81490328526868</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="B122" t="n">
+        <v>69.70522136500185</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="B123" t="n">
+        <v>69.60469000482757</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>34</v>
+      </c>
+      <c r="B124" t="n">
+        <v>69.51385107191973</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="B125" t="n">
+        <v>69.43320142076901</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="B126" t="n">
+        <v>69.36319025323088</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="B127" t="n">
+        <v>69.30421669804309</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>35</v>
+      </c>
+      <c r="B128" t="n">
+        <v>69.25662762223124</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="B129" t="n">
+        <v>69.22071568578208</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="B130" t="n">
+        <v>69.19671764987369</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="B131" t="n">
+        <v>69.18481294780877</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>36</v>
+      </c>
+      <c r="B132" t="n">
+        <v>69.18512252661279</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="B133" t="n">
+        <v>69.1977079660316</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="B134" t="n">
+        <v>69.22257088040281</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>36.75</v>
+      </c>
+      <c r="B135" t="n">
+        <v>69.25965260758532</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>37</v>
+      </c>
+      <c r="B136" t="n">
+        <v>69.30883418781698</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="B137" t="n">
+        <v>69.36993663403716</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="B138" t="n">
+        <v>69.44272149386521</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="B139" t="n">
+        <v>69.52689170207172</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>38</v>
+      </c>
+      <c r="B140" t="n">
+        <v>69.62209272102375</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="B141" t="n">
+        <v>69.7279139652339</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="B142" t="n">
+        <v>69.84389050480058</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="B143" t="n">
+        <v>69.96950504120038</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>39</v>
+      </c>
+      <c r="B144" t="n">
+        <v>70.10419014758736</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="B145" t="n">
+        <v>70.24733076447575</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="B146" t="n">
+        <v>70.39826694043498</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="B147" t="n">
+        <v>70.55629680621769</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>40</v>
+      </c>
+      <c r="B148" t="n">
+        <v>70.72067976957563</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="B149" t="n">
+        <v>70.89063991690114</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="B150" t="n">
+        <v>71.06536960676883</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="B151" t="n">
+        <v>71.24403323944759</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>41</v>
+      </c>
+      <c r="B152" t="n">
+        <v>71.42577118551354</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="B153" t="n">
+        <v>71.60970385582246</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="B154" t="n">
+        <v>71.79493589430332</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>41.75</v>
+      </c>
+      <c r="B155" t="n">
+        <v>71.98056047431332</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>42</v>
+      </c>
+      <c r="B156" t="n">
+        <v>72.16566367865639</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="B157" t="n">
+        <v>72.34932894281319</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="B158" t="n">
+        <v>72.53064154046518</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="B159" t="n">
+        <v>72.70869309002197</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>43</v>
+      </c>
+      <c r="B160" t="n">
+        <v>72.88258606058154</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="B161" t="n">
+        <v>73.0514382555707</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="B162" t="n">
+        <v>73.21438725222873</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="B163" t="n">
+        <v>73.37059477511481</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>44</v>
+      </c>
+      <c r="B164" t="n">
+        <v>73.51925098193701</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="B165" t="n">
+        <v>73.65957864022312</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="B166" t="n">
+        <v>73.79083717367654</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>44.75</v>
+      </c>
+      <c r="B167" t="n">
+        <v>73.91232655748802</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>45</v>
+      </c>
+      <c r="B168" t="n">
+        <v>74.02339104240382</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="B169" t="n">
+        <v>74.12342268798116</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="B170" t="n">
+        <v>74.21186468619344</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>45.75</v>
+      </c>
+      <c r="B171" t="n">
+        <v>74.28821445737641</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>46</v>
+      </c>
+      <c r="B172" t="n">
+        <v>74.35202650143133</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>46.25</v>
+      </c>
+      <c r="B173" t="n">
+        <v>74.4029149882181</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="B174" t="n">
+        <v>74.44055607217818</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="B175" t="n">
+        <v>74.46468991741783</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>47</v>
+      </c>
+      <c r="B176" t="n">
+        <v>74.47512242075477</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="B177" t="n">
+        <v>74.47172662157892</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="B178" t="n">
+        <v>74.45444378879642</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="B179" t="n">
+        <v>74.42328417660976</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>48</v>
+      </c>
+      <c r="B180" t="n">
+        <v>74.37832744242937</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="B181" t="n">
+        <v>74.31972272180774</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="B182" t="n">
+        <v>74.24768835692785</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="B183" t="n">
+        <v>74.16251127685783</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>49</v>
+      </c>
+      <c r="B184" t="n">
+        <v>74.06454602949351</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="B185" t="n">
+        <v>73.95421346684387</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="B186" t="n">
+        <v>73.8319990870616</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="B187" t="n">
+        <v>73.69845103837484</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>50</v>
+      </c>
+      <c r="B188" t="n">
+        <v>73.55417779182687</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="B189" t="n">
+        <v>73.3998454914701</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="B190" t="n">
+        <v>73.23617499237915</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="B191" t="n">
+        <v>73.06393859853718</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>51</v>
+      </c>
+      <c r="B192" t="n">
+        <v>72.88395651430056</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="B193" t="n">
+        <v>72.69709302474968</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="B194" t="n">
+        <v>72.50425242178115</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="B195" t="n">
+        <v>72.30637469427784</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>52</v>
+      </c>
+      <c r="B196" t="n">
+        <v>72.10443100210047</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="B197" t="n">
+        <v>71.89941895496986</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="B198" t="n">
+        <v>71.69235771854261</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="B199" t="n">
+        <v>71.48428297111943</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>53</v>
+      </c>
+      <c r="B200" t="n">
+        <v>71.27624173545424</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="B201" t="n">
+        <v>71.06928711104939</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="B202" t="n">
+        <v>70.86447293311836</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="B203" t="n">
+        <v>70.66284838506851</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>54</v>
+      </c>
+      <c r="B204" t="n">
+        <v>70.46545259189568</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>54.25</v>
+      </c>
+      <c r="B205" t="n">
+        <v>70.27330922228494</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="B206" t="n">
+        <v>70.08742112747434</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="B207" t="n">
+        <v>69.90876504505594</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>55</v>
+      </c>
+      <c r="B208" t="n">
+        <v>69.73828639585903</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="B209" t="n">
+        <v>69.57689420188204</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="B210" t="n">
+        <v>69.42545615290973</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="B211" t="n">
+        <v>69.28479384897211</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>56</v>
+      </c>
+      <c r="B212" t="n">
+        <v>69.15567824516951</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="B213" t="n">
+        <v>69.03882532460699</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="B214" t="n">
+        <v>68.93489202425171</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="B215" t="n">
+        <v>68.84447243745223</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>57</v>
+      </c>
+      <c r="B216" t="n">
+        <v>68.76809431564321</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="B217" t="n">
+        <v>68.70621589040587</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="B218" t="n">
+        <v>68.65922303557062</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="B219" t="n">
+        <v>68.62742678743955</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>58</v>
+      </c>
+      <c r="B220" t="n">
+        <v>68.61106123947926</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="B221" t="n">
+        <v>68.61028182599773</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="B222" t="n">
+        <v>68.62516400738092</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="B223" t="n">
+        <v>68.6557023674343</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>59</v>
+      </c>
+      <c r="B224" t="n">
+        <v>68.70181013126238</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="B225" t="n">
+        <v>68.76331910993436</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="B226" t="n">
+        <v>68.83998007594003</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="B227" t="n">
+        <v>68.931463571146</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>60</v>
+      </c>
+      <c r="B228" t="n">
+        <v>69.03736114663266</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="B229" t="n">
+        <v>69.15718703143841</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="B230" t="n">
+        <v>69.29038022487249</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="B231" t="n">
+        <v>69.43630700469539</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>61</v>
+      </c>
+      <c r="B232" t="n">
+        <v>69.59426384111813</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="B233" t="n">
+        <v>69.76348070425389</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="B234" t="n">
+        <v>69.94312475037951</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="B235" t="n">
+        <v>70.13230437014458</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>62</v>
+      </c>
+      <c r="B236" t="n">
+        <v>70.33007357971547</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="B237" t="n">
+        <v>70.53543673377339</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="B238" t="n">
+        <v>70.74735353731265</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>62.75</v>
+      </c>
+      <c r="B239" t="n">
+        <v>70.96474433132063</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>63</v>
+      </c>
+      <c r="B240" t="n">
+        <v>71.18649562567504</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="B241" t="n">
+        <v>71.41146585097991</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="B242" t="n">
+        <v>71.63849129958948</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="B243" t="n">
+        <v>71.86639222474919</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>64</v>
+      </c>
+      <c r="B244" t="n">
+        <v>72.09397906562546</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="B245" t="n">
+        <v>72.32005876500871</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="B246" t="n">
+        <v>72.54344114566598</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="B247" t="n">
+        <v>72.76294531069554</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>65</v>
+      </c>
+      <c r="B248" t="n">
+        <v>72.97740603280332</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="B249" t="n">
+        <v>73.18568009718282</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="B250" t="n">
+        <v>73.38665256264245</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>65.75</v>
+      </c>
+      <c r="B251" t="n">
+        <v>73.57924290578572</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>66</v>
+      </c>
+      <c r="B252" t="n">
+        <v>73.7624110134161</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>66.25</v>
+      </c>
+      <c r="B253" t="n">
+        <v>73.93516298890601</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="B254" t="n">
+        <v>74.0965567390393</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="B255" t="n">
+        <v>74.24570730880595</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>67</v>
+      </c>
+      <c r="B256" t="n">
+        <v>74.38179193279268</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="B257" t="n">
+        <v>74.50405477316889</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="B258" t="n">
+        <v>74.61181131580889</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="B259" t="n">
+        <v>74.70445239780946</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>68</v>
+      </c>
+      <c r="B260" t="n">
+        <v>74.78144784155057</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="B261" t="n">
+        <v>74.84234967249532</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="B262" t="n">
+        <v>74.88679490012343</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="B263" t="n">
+        <v>74.91450784372918</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>69</v>
+      </c>
+      <c r="B264" t="n">
+        <v>74.92530198727644</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="B265" t="n">
+        <v>74.9190813500782</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="B266" t="n">
+        <v>74.89584136273979</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="B267" t="n">
+        <v>74.8556692405603</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>70</v>
+      </c>
+      <c r="B268" t="n">
+        <v>74.79874384940919</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="B269" t="n">
+        <v>74.72533506196896</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="B270" t="n">
+        <v>74.63580260514324</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>70.75</v>
+      </c>
+      <c r="B271" t="n">
+        <v>74.53059440235546</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>71</v>
+      </c>
+      <c r="B272" t="n">
+        <v>74.41024441739025</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="B273" t="n">
+        <v>74.27537000933826</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="B274" t="n">
+        <v>74.12666881108062</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="B275" t="n">
+        <v>73.96491514657073</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>72</v>
+      </c>
+      <c r="B276" t="n">
+        <v>73.79095600492518</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="B277" t="n">
+        <v>73.60570659200158</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="B278" t="n">
+        <v>73.41014548270493</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>72.75</v>
+      </c>
+      <c r="B279" t="n">
+        <v>73.20530939970845</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>73</v>
+      </c>
+      <c r="B280" t="n">
+        <v>72.99228764658369</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="B281" t="n">
+        <v>72.77221622549514</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="B282" t="n">
+        <v>72.54627167160938</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="B283" t="n">
+        <v>72.31566463818838</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>74</v>
+      </c>
+      <c r="B284" t="n">
+        <v>72.08163326796578</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="B285" t="n">
+        <v>71.8454363878338</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="B286" t="n">
+        <v>71.60834656508754</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="B287" t="n">
+        <v>71.37164306447212</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>75</v>
+      </c>
+      <c r="B288" t="n">
+        <v>71.13660474605021</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="B289" t="n">
+        <v>70.90450294444695</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="B290" t="n">
+        <v>70.67659437032931</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="B291" t="n">
+        <v>70.45411407503738</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>76</v>
+      </c>
+      <c r="B292" t="n">
+        <v>70.2382685191005</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="B293" t="n">
+        <v>70.03022878494441</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="B294" t="n">
+        <v>69.83112397342491</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="B295" t="n">
+        <v>69.64203482291401</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>77</v>
+      </c>
+      <c r="B296" t="n">
+        <v>69.46398758851846</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="B297" t="n">
+        <v>69.2979482176344</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="B298" t="n">
+        <v>69.14481685644276</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="B299" t="n">
+        <v>69.00542272013602</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>78</v>
+      </c>
+      <c r="B300" t="n">
+        <v>68.8805193576475</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="B301" t="n">
+        <v>68.7707803394416</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="B302" t="n">
+        <v>68.67679539452888</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="B303" t="n">
+        <v>68.59906702030769</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>79</v>
+      </c>
+      <c r="B304" t="n">
+        <v>68.53800758611841</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="B305" t="n">
+        <v>68.49393694854457</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="B306" t="n">
+        <v>68.46708059352127</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="B307" t="n">
+        <v>68.45756831723665</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>80</v>
+      </c>
+      <c r="B308" t="n">
+        <v>68.46543345465096</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>80.25</v>
+      </c>
+      <c r="B309" t="n">
+        <v>68.49061266123299</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="B310" t="n">
+        <v>68.53294625024158</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="B311" t="n">
+        <v>68.59217908458274</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>81</v>
+      </c>
+      <c r="B312" t="n">
+        <v>68.66796201896933</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="B313" t="n">
+        <v>68.75985388482211</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="B314" t="n">
+        <v>68.86732400709691</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>81.75</v>
+      </c>
+      <c r="B315" t="n">
+        <v>68.98975523902504</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>82</v>
+      </c>
+      <c r="B316" t="n">
+        <v>69.12644749763011</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="B317" t="n">
+        <v>69.27662177985658</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="B318" t="n">
+        <v>69.43942463623056</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="B319" t="n">
+        <v>69.6139330761907</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>83</v>
+      </c>
+      <c r="B320" t="n">
+        <v>69.79915987659577</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="B321" t="n">
+        <v>69.99405926244891</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="B322" t="n">
+        <v>70.19753292659803</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="B323" t="n">
+        <v>70.40843635308552</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>84</v>
+      </c>
+      <c r="B324" t="n">
+        <v>70.62558540694883</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="B325" t="n">
+        <v>70.84776315162254</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="B326" t="n">
+        <v>71.07372685367847</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="B327" t="n">
+        <v>71.30221513346801</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>85</v>
+      </c>
+      <c r="B328" t="n">
+        <v>71.53195521931225</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="B329" t="n">
+        <v>71.76167026222309</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="B330" t="n">
+        <v>71.99008666774085</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="B331" t="n">
+        <v>72.21594140134121</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>86</v>
+      </c>
+      <c r="B332" t="n">
+        <v>72.43798922399958</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>86.25</v>
+      </c>
+      <c r="B333" t="n">
+        <v>72.65500981490428</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="B334" t="n">
+        <v>72.86581473897752</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="B335" t="n">
+        <v>73.06925421779339</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>87</v>
+      </c>
+      <c r="B336" t="n">
+        <v>73.26422366366783</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="B337" t="n">
+        <v>73.44966993813094</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="B338" t="n">
+        <v>73.62459729766742</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>87.75</v>
+      </c>
+      <c r="B339" t="n">
+        <v>73.788072991517</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>88</v>
+      </c>
+      <c r="B340" t="n">
+        <v>73.93923247845083</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="B341" t="n">
+        <v>74.07728423176999</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="B342" t="n">
+        <v>74.20151410429358</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="B343" t="n">
+        <v>74.31128922780195</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>89</v>
+      </c>
+      <c r="B344" t="n">
+        <v>74.40606142425699</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="B345" t="n">
+        <v>74.48537010912025</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="B346" t="n">
+        <v>74.5488446702104</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>89.75</v>
+      </c>
+      <c r="B347" t="n">
+        <v>74.59620630876542</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>90</v>
+      </c>
+      <c r="B348" t="n">
+        <v>74.62726933268179</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="B349" t="n">
+        <v>74.64194189527031</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="B350" t="n">
+        <v>74.640226176277</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="B351" t="n">
+        <v>74.62221800534397</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>91</v>
+      </c>
+      <c r="B352" t="n">
+        <v>74.58810593150871</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="B353" t="n">
+        <v>74.53816974573874</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="B354" t="n">
+        <v>74.47277846685066</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="B355" t="n">
+        <v>74.39238780444643</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>92</v>
+      </c>
+      <c r="B356" t="n">
+        <v>74.29753711569538</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>92.25</v>
+      </c>
+      <c r="B357" t="n">
+        <v>74.18884587587539</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="B358" t="n">
+        <v>74.06700968554446</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>92.75</v>
+      </c>
+      <c r="B359" t="n">
+        <v>73.932795840022</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>93</v>
+      </c>
+      <c r="B360" t="n">
+        <v>73.78703848950244</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="B361" t="n">
+        <v>73.63063342058436</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="B362" t="n">
+        <v>73.46453249225985</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="B363" t="n">
+        <v>73.2897377614586</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>94</v>
+      </c>
+      <c r="B364" t="n">
+        <v>73.10729533506471</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="B365" t="n">
+        <v>72.91828898691112</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="B366" t="n">
+        <v>72.72383357959642</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="B367" t="n">
+        <v>72.52506833205375</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>95</v>
+      </c>
+      <c r="B368" t="n">
+        <v>72.32314997462477</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>95.25</v>
+      </c>
+      <c r="B369" t="n">
+        <v>72.11924583394834</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="B370" t="n">
+        <v>71.91452689026049</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="B371" t="n">
+        <v>71.71016084971841</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>96</v>
+      </c>
+      <c r="B372" t="n">
+        <v>71.5073052741065</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="B373" t="n">
+        <v>71.30710080975985</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="B374" t="n">
+        <v>71.11066455675309</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="B375" t="n">
+        <v>70.91908361835752</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>97</v>
+      </c>
+      <c r="B376" t="n">
+        <v>70.73340886947184</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="B377" t="n">
+        <v>70.55464898119355</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="B378" t="n">
+        <v>70.38376473692638</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="B379" t="n">
+        <v>70.2216636734301</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>98</v>
+      </c>
+      <c r="B380" t="n">
+        <v>70.06919507802139</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="B381" t="n">
+        <v>69.92714537074906</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>98.5</v>
+      </c>
+      <c r="B382" t="n">
+        <v>69.7962338978036</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>98.75</v>
+      </c>
+      <c r="B383" t="n">
+        <v>69.67710915970304</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>99</v>
+      </c>
+      <c r="B384" t="n">
+        <v>69.57034549493773</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="B385" t="n">
+        <v>69.47644023677854</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="B386" t="n">
+        <v>69.395811357874</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="B387" t="n">
+        <v>69.3287956141033</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>100</v>
+      </c>
+      <c r="B388" t="n">
+        <v>69.27564719593521</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>100.25</v>
+      </c>
+      <c r="B389" t="n">
+        <v>69.23653689228786</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="B390" t="n">
+        <v>69.21155176861429</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>100.75</v>
+      </c>
+      <c r="B391" t="n">
+        <v>69.20069535767385</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>101</v>
+      </c>
+      <c r="B392" t="n">
+        <v>69.20388835821205</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="B393" t="n">
+        <v>69.22096983358246</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="B394" t="n">
+        <v>69.25169889922472</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>101.75</v>
+      </c>
+      <c r="B395" t="n">
+        <v>69.2957568848821</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>102</v>
+      </c>
+      <c r="B396" t="n">
+        <v>69.35274995452011</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>102.25</v>
+      </c>
+      <c r="B397" t="n">
+        <v>69.42221216411374</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="B398" t="n">
+        <v>69.50360893482143</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="B399" t="n">
+        <v>69.59634091657722</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>103</v>
+      </c>
+      <c r="B400" t="n">
+        <v>69.69974821482269</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="B401" t="n">
+        <v>69.81311495098329</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="B402" t="n">
+        <v>69.93567412538037</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="B403" t="n">
+        <v>70.06661274957395</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>104</v>
+      </c>
+      <c r="B404" t="n">
+        <v>70.20507721366066</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="B405" t="n">
+        <v>70.35017885281599</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="B406" t="n">
+        <v>70.50099967637526</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="B407" t="n">
+        <v>70.65659822200051</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>105</v>
+      </c>
+      <c r="B408" t="n">
+        <v>70.81601549698264</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>105.25</v>
+      </c>
+      <c r="B409" t="n">
+        <v>70.97828096848205</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="B410" t="n">
+        <v>71.1424185645167</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>105.75</v>
+      </c>
+      <c r="B411" t="n">
+        <v>71.30745264776209</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>106</v>
+      </c>
+      <c r="B412" t="n">
+        <v>71.4724139247291</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="B413" t="n">
+        <v>71.63634525362934</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="B414" t="n">
+        <v>71.79830731521547</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="B415" t="n">
+        <v>71.95738411208886</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>107</v>
+      </c>
+      <c r="B416" t="n">
+        <v>72.11268826338879</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="B417" t="n">
+        <v>72.26336606340453</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="B418" t="n">
+        <v>72.40860227447227</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="B419" t="n">
+        <v>72.54762462651964</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>108</v>
+      </c>
+      <c r="B420" t="n">
+        <v>72.67970799778477</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="B421" t="n">
+        <v>72.80417825355184</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="B422" t="n">
+        <v>72.92041572219009</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="B423" t="n">
+        <v>73.02785829034509</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>109</v>
+      </c>
+      <c r="B424" t="n">
+        <v>73.12600410178685</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="B425" t="n">
+        <v>73.21441384715465</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="B426" t="n">
+        <v>73.29271263463103</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="B427" t="n">
+        <v>73.36059143440933</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>110</v>
+      </c>
+      <c r="B428" t="n">
+        <v>73.41780809267109</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>110.25</v>
+      </c>
+      <c r="B429" t="n">
+        <v>73.46418791364201</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="B430" t="n">
+        <v>73.49962381112826</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>110.75</v>
+      </c>
+      <c r="B431" t="n">
+        <v>73.52407603373078</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>111</v>
+      </c>
+      <c r="B432" t="n">
+        <v>73.53757147067373</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="B433" t="n">
+        <v>73.54020254784811</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="B434" t="n">
+        <v>73.53212572624369</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>111.75</v>
+      </c>
+      <c r="B435" t="n">
+        <v>73.51355961740633</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>112</v>
+      </c>
+      <c r="B436" t="n">
+        <v>73.48478273289733</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>112.25</v>
+      </c>
+      <c r="B437" t="n">
+        <v>73.44613088693205</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="B438" t="n">
+        <v>73.39799427342305</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="B439" t="n">
+        <v>73.34081424053558</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>113</v>
+      </c>
+      <c r="B440" t="n">
+        <v>73.27507978757066</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="B441" t="n">
+        <v>73.20132381051128</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="B442" t="n">
+        <v>73.12011912389443</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>113.75</v>
+      </c>
+      <c r="B443" t="n">
+        <v>73.03207428779682</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>114</v>
+      </c>
+      <c r="B444" t="n">
+        <v>72.93782926964076</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="B445" t="n">
+        <v>72.83805097123441</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="B446" t="n">
+        <v>72.73342865195487</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="B447" t="n">
+        <v>72.62466927926181</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>115</v>
+      </c>
+      <c r="B448" t="n">
+        <v>72.51249283779575</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>115.25</v>
+      </c>
+      <c r="B449" t="n">
+        <v>72.39762762816781</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="B450" t="n">
+        <v>72.28080558619351</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>115.75</v>
+      </c>
+      <c r="B451" t="n">
+        <v>72.16275765276443</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>116</v>
+      </c>
+      <c r="B452" t="n">
+        <v>72.04420922379542</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="B453" t="n">
+        <v>71.92587570873988</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="B454" t="n">
+        <v>71.80845822503815</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="B455" t="n">
+        <v>71.69263945456746</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>117</v>
+      </c>
+      <c r="B456" t="n">
+        <v>71.57907968670318</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>117.25</v>
+      </c>
+      <c r="B457" t="n">
+        <v>71.46841307099687</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="B458" t="n">
+        <v>71.36124410073587</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="B459" t="n">
+        <v>71.25814434678838</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>118</v>
+      </c>
+      <c r="B460" t="n">
+        <v>71.15964945917061</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="B461" t="n">
+        <v>71.06625645171343</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="B462" t="n">
+        <v>70.97842128307097</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="B463" t="n">
+        <v>70.89655674511893</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>119</v>
+      </c>
+      <c r="B464" t="n">
+        <v>70.8210306675508</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="B465" t="n">
+        <v>70.75216444521423</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="B466" t="n">
+        <v>70.69023189245088</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>119.75</v>
+      </c>
+      <c r="B467" t="n">
+        <v>70.63545842642961</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>120</v>
+      </c>
+      <c r="B468" t="n">
+        <v>70.5880205792099</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>120.25</v>
+      </c>
+      <c r="B469" t="n">
+        <v>70.5480458360548</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="B470" t="n">
+        <v>70.51561279534603</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>120.75</v>
+      </c>
+      <c r="B471" t="n">
+        <v>70.49075164335365</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>121</v>
+      </c>
+      <c r="B472" t="n">
+        <v>70.47344493508987</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>121.25</v>
+      </c>
+      <c r="B473" t="n">
+        <v>70.46362867054779</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="B474" t="n">
+        <v>70.46119365380005</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>121.75</v>
+      </c>
+      <c r="B475" t="n">
+        <v>70.46598712072364</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>122</v>
+      </c>
+      <c r="B476" t="n">
+        <v>70.47781461953312</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>122.25</v>
+      </c>
+      <c r="B477" t="n">
+        <v>70.49644212685745</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="B478" t="n">
+        <v>70.52159838079055</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="B479" t="n">
+        <v>70.55297741119256</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>123</v>
+      </c>
+      <c r="B480" t="n">
+        <v>70.59024124652119</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>123.25</v>
+      </c>
+      <c r="B481" t="n">
+        <v>70.63302277563665</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="B482" t="n">
+        <v>70.68092874235177</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>123.75</v>
+      </c>
+      <c r="B483" t="n">
+        <v>70.73354284999395</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>124</v>
+      </c>
+      <c r="B484" t="n">
+        <v>70.7904289529086</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>124.25</v>
+      </c>
+      <c r="B485" t="n">
+        <v>70.85113431166303</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="B486" t="n">
+        <v>70.91519288870636</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="B487" t="n">
+        <v>70.98212866139903</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>125</v>
+      </c>
+      <c r="B488" t="n">
+        <v>71.05145892964474</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>125.25</v>
+      </c>
+      <c r="B489" t="n">
+        <v>71.12269759582956</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="B490" t="n">
+        <v>71.19535839539459</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>125.75</v>
+      </c>
+      <c r="B491" t="n">
+        <v>71.26895805713092</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>126</v>
+      </c>
+      <c r="B492" t="n">
+        <v>71.343019373182</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="B493" t="n">
+        <v>71.41707415976002</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="B494" t="n">
+        <v>71.49066609071876</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="B495" t="n">
+        <v>71.56335338736825</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>127</v>
+      </c>
+      <c r="B496" t="n">
+        <v>71.63471134925193</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>127.25</v>
+      </c>
+      <c r="B497" t="n">
+        <v>71.70433471202725</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>127.5</v>
+      </c>
+      <c r="B498" t="n">
+        <v>71.77183982008115</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>127.75</v>
+      </c>
+      <c r="B499" t="n">
+        <v>71.8368666030628</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>128</v>
+      </c>
+      <c r="B500" t="n">
+        <v>71.89908034711348</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="B501" t="n">
+        <v>71.95817325320715</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="B502" t="n">
+        <v>72.01386577666977</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="B503" t="n">
+        <v>72.06590774361203</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>129</v>
+      </c>
+      <c r="B504" t="n">
+        <v>72.1140792416726</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>129.25</v>
+      </c>
+      <c r="B505" t="n">
+        <v>72.15819128411842</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="B506" t="n">
+        <v>72.19808624797047</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="n">
+        <v>129.75</v>
+      </c>
+      <c r="B507" t="n">
+        <v>72.2336380884083</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="n">
+        <v>130</v>
+      </c>
+      <c r="B508" t="n">
+        <v>72.2647523332421</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="n">
+        <v>130.25</v>
+      </c>
+      <c r="B509" t="n">
+        <v>72.29136586271844</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="B510" t="n">
+        <v>72.31344648133265</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="B511" t="n">
+        <v>72.33099228965187</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>131</v>
+      </c>
+      <c r="B512" t="n">
+        <v>72.34403086539538</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>131.25</v>
+      </c>
+      <c r="B513" t="n">
+        <v>72.35261826416888</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="B514" t="n">
+        <v>72.35683785129827</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>131.75</v>
+      </c>
+      <c r="B515" t="n">
+        <v>72.35679897715123</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>132</v>
+      </c>
+      <c r="B516" t="n">
+        <v>72.35263550916662</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>132.25</v>
+      </c>
+      <c r="B517" t="n">
+        <v>72.34450423452849</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="B518" t="n">
+        <v>72.33258314802129</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>132.75</v>
+      </c>
+      <c r="B519" t="n">
+        <v>72.31706964008161</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>133</v>
+      </c>
+      <c r="B520" t="n">
+        <v>72.29817860042068</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>133.25</v>
+      </c>
+      <c r="B521" t="n">
+        <v>72.27614045282832</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="B522" t="n">
+        <v>72.25119913688614</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>133.75</v>
+      </c>
+      <c r="B523" t="n">
+        <v>72.22361005231573</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>134</v>
+      </c>
+      <c r="B524" t="n">
+        <v>72.19363798156945</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>134.25</v>
+      </c>
+      <c r="B525" t="n">
+        <v>72.16155500604182</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="B526" t="n">
+        <v>72.12763843094102</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>134.75</v>
+      </c>
+      <c r="B527" t="n">
+        <v>72.09216873341825</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>135</v>
+      </c>
+      <c r="B528" t="n">
+        <v>72.055427548013</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>135.25</v>
+      </c>
+      <c r="B529" t="n">
+        <v>72.01769570284075</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="B530" t="n">
+        <v>71.97925131923286</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>135.75</v>
+      </c>
+      <c r="B531" t="n">
+        <v>71.94036798674416</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>136</v>
+      </c>
+      <c r="B532" t="n">
+        <v>71.90131302457939</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>136.25</v>
+      </c>
+      <c r="B533" t="n">
+        <v>71.86234583956282</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="B534" t="n">
+        <v>71.8237163897964</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>136.75</v>
+      </c>
+      <c r="B535" t="n">
+        <v>71.78566376212669</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>137</v>
+      </c>
+      <c r="B536" t="n">
+        <v>71.748414870481</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="B537" t="n">
+        <v>71.71218328104638</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="B538" t="n">
+        <v>71.67716816916052</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>137.75</v>
+      </c>
+      <c r="B539" t="n">
+        <v>71.6435534116706</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>138</v>
+      </c>
+      <c r="B540" t="n">
+        <v>71.61150681740307</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="n">
+        <v>138.25</v>
+      </c>
+      <c r="B541" t="n">
+        <v>71.58117949728306</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="B542" t="n">
+        <v>71.55270537455431</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>138.75</v>
+      </c>
+      <c r="B543" t="n">
+        <v>71.52620083448828</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>139</v>
+      </c>
+      <c r="B544" t="n">
+        <v>71.50176451194116</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="n">
+        <v>139.25</v>
+      </c>
+      <c r="B545" t="n">
+        <v>71.4794772141267</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="B546" t="n">
+        <v>71.45940197502964</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="n">
+        <v>139.75</v>
+      </c>
+      <c r="B547" t="n">
+        <v>71.44158423699291</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="n">
+        <v>140</v>
+      </c>
+      <c r="B548" t="n">
+        <v>71.42605215417953</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>140.25</v>
+      </c>
+      <c r="B549" t="n">
+        <v>71.41281701183973</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="B550" t="n">
+        <v>71.40187375461301</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="n">
+        <v>140.75</v>
+      </c>
+      <c r="B551" t="n">
+        <v>71.39320161646356</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>141</v>
+      </c>
+      <c r="B552" t="n">
+        <v>71.38676484429273</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="n">
+        <v>141.25</v>
+      </c>
+      <c r="B553" t="n">
+        <v>71.38251350679279</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="B554" t="n">
+        <v>71.38038437970748</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>141.75</v>
+      </c>
+      <c r="B555" t="n">
+        <v>71.38030189834485</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>142</v>
+      </c>
+      <c r="B556" t="n">
+        <v>71.38217916794947</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>142.25</v>
+      </c>
+      <c r="B557" t="n">
+        <v>71.38591902238218</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>142.5</v>
+      </c>
+      <c r="B558" t="n">
+        <v>71.39141512147656</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="n">
+        <v>142.75</v>
+      </c>
+      <c r="B559" t="n">
+        <v>71.39855307743998</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>143</v>
+      </c>
+      <c r="B560" t="n">
+        <v>71.40721160074175</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>143.25</v>
+      </c>
+      <c r="B561" t="n">
+        <v>71.41726365607811</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="B562" t="n">
+        <v>71.4285776192221</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>143.75</v>
+      </c>
+      <c r="B563" t="n">
+        <v>71.44101842584963</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="n">
+        <v>144</v>
+      </c>
+      <c r="B564" t="n">
+        <v>71.45444870377946</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="B565" t="n">
+        <v>71.46872988046843</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>144.5</v>
+      </c>
+      <c r="B566" t="n">
+        <v>71.48372325805968</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>144.75</v>
+      </c>
+      <c r="B567" t="n">
+        <v>71.49929104878579</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="n">
+        <v>145</v>
+      </c>
+      <c r="B568" t="n">
+        <v>71.51529736407505</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="n">
+        <v>145.25</v>
+      </c>
+      <c r="B569" t="n">
+        <v>71.53160915129268</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="B570" t="n">
+        <v>71.54809707266274</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>145.75</v>
+      </c>
+      <c r="B571" t="n">
+        <v>71.56463632155692</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="n">
+        <v>146</v>
+      </c>
+      <c r="B572" t="n">
+        <v>71.58110737199509</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="n">
+        <v>146.25</v>
+      </c>
+      <c r="B573" t="n">
+        <v>71.59739665787583</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="n">
+        <v>146.5</v>
+      </c>
+      <c r="B574" t="n">
+        <v>71.61339717913508</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="n">
+        <v>146.75</v>
+      </c>
+      <c r="B575" t="n">
+        <v>71.62900903271358</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="n">
+        <v>147</v>
+      </c>
+      <c r="B576" t="n">
+        <v>71.64413986689168</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="n">
+        <v>147.25</v>
+      </c>
+      <c r="B577" t="n">
+        <v>71.65870525821862</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="B578" t="n">
+        <v>71.67262901091766</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>147.75</v>
+      </c>
+      <c r="B579" t="n">
+        <v>71.68584337928235</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>148</v>
+      </c>
+      <c r="B580" t="n">
+        <v>71.69828921418866</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>148.25</v>
+      </c>
+      <c r="B581" t="n">
+        <v>71.70991603542913</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="B582" t="n">
+        <v>71.7206820321223</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>148.75</v>
+      </c>
+      <c r="B583" t="n">
+        <v>71.73055399396281</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>149</v>
+      </c>
+      <c r="B584" t="n">
+        <v>71.73950717654945</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>149.25</v>
+      </c>
+      <c r="B585" t="n">
+        <v>71.74752510445742</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>149.5</v>
+      </c>
+      <c r="B586" t="n">
+        <v>71.75459931610673</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>149.75</v>
+      </c>
+      <c r="B587" t="n">
+        <v>71.76072905481645</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>150</v>
+      </c>
+      <c r="B588" t="n">
+        <v>71.76592091072446</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="B589" t="n">
+        <v>71.77018841849416</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>150.5</v>
+      </c>
+      <c r="B590" t="n">
+        <v>71.77355161592006</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>150.75</v>
+      </c>
+      <c r="B591" t="n">
+        <v>71.77603656868652</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>151</v>
+      </c>
+      <c r="B592" t="n">
+        <v>71.77767486662549</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="B593" t="n">
+        <v>71.77850309686274</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="B594" t="n">
+        <v>71.77856229923766</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="B595" t="n">
+        <v>71.77789740933136</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>152</v>
+      </c>
+      <c r="B596" t="n">
+        <v>71.77655669434321</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>152.25</v>
+      </c>
+      <c r="B597" t="n">
+        <v>71.77459118691937</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>152.5</v>
+      </c>
+      <c r="B598" t="n">
+        <v>71.77205412186085</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>152.75</v>
+      </c>
+      <c r="B599" t="n">
+        <v>71.76900038042609</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>153</v>
+      </c>
+      <c r="B600" t="n">
+        <v>71.76548594669633</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>153.25</v>
+      </c>
+      <c r="B601" t="n">
+        <v>71.76156738019526</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>153.5</v>
+      </c>
+      <c r="B602" t="n">
+        <v>71.75730130865064</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>153.75</v>
+      </c>
+      <c r="B603" t="n">
+        <v>71.75274394445727</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>154</v>
+      </c>
+      <c r="B604" t="n">
+        <v>71.74795062805359</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="n">
+        <v>154.25</v>
+      </c>
+      <c r="B605" t="n">
+        <v>71.74297540105945</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="B606" t="n">
+        <v>71.73787061164619</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="n">
+        <v>154.75</v>
+      </c>
+      <c r="B607" t="n">
+        <v>71.73268655422423</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>155</v>
+      </c>
+      <c r="B608" t="n">
+        <v>71.7274711451429</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="n">
+        <v>155.25</v>
+      </c>
+      <c r="B609" t="n">
+        <v>71.72226963570463</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="B610" t="n">
+        <v>71.71712436340594</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>155.75</v>
+      </c>
+      <c r="B611" t="n">
+        <v>71.71207454193272</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -64839,7 +69812,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -65043,7 +70016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -65125,7 +70098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
